--- a/05_metadata/AI_质检实验题库_实验一实验二_多目标采购版.xlsx
+++ b/05_metadata/AI_质检实验题库_实验一实验二_多目标采购版.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\streamlit_mvtec_experiment\05_metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9317007B-E0E6-44B8-A704-A14129DF0BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E5D2668-29F4-43E5-A53C-7B40A4D1C652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -1283,9 +1283,6 @@
     <t>practice/1_002.png</t>
   </si>
   <si>
-    <t>正确答案：NG（不合格）。AI 认为该瓶子为 OK（合格），依据是图像中未见明显异常，产品外观与标准样本一致。</t>
-  </si>
-  <si>
     <t>practice/1_003.png</t>
   </si>
   <si>
@@ -1338,6 +1335,10 @@
   </si>
   <si>
     <t>标准答案：不采购。质量分=72，成本分=64.6，综合分=69.8。先检查质量是否过线，再综合考虑成本。</t>
+  </si>
+  <si>
+    <t>正确答案：NG（不合格）。AI 认为该瓶子为 NG（不合格），依据是图像中可见明显异常，产品外观有污染缺陷，与标准样本不一致。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2166,6 +2167,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S51"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="15" max="15" width="95.6328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="101" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="170.08984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -9303,6 +9309,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="14" max="14" width="110.7265625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -9444,7 +9453,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="s">
-        <v>419</v>
+        <v>437</v>
       </c>
       <c r="O5" t="s">
         <v>417</v>
@@ -9473,7 +9482,7 @@
         <v>114</v>
       </c>
       <c r="H6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I6" t="s">
         <v>415</v>
@@ -9491,7 +9500,7 @@
         <v>1</v>
       </c>
       <c r="N6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="O6" t="s">
         <v>417</v>
@@ -9520,7 +9529,7 @@
         <v>153</v>
       </c>
       <c r="H7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I7" t="s">
         <v>415</v>
@@ -9538,7 +9547,7 @@
         <v>1</v>
       </c>
       <c r="N7" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="O7" t="s">
         <v>417</v>
@@ -9549,13 +9558,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
+        <v>423</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
         <v>424</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
-        <v>425</v>
       </c>
       <c r="E8" t="s">
         <v>112</v>
@@ -9567,10 +9576,10 @@
         <v>114</v>
       </c>
       <c r="H8" t="s">
+        <v>425</v>
+      </c>
+      <c r="I8" t="s">
         <v>426</v>
-      </c>
-      <c r="I8" t="s">
-        <v>427</v>
       </c>
       <c r="J8" t="s">
         <v>323</v>
@@ -9585,7 +9594,7 @@
         <v>1</v>
       </c>
       <c r="N8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="O8" t="s">
         <v>417</v>
@@ -9596,13 +9605,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C9">
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E9" t="s">
         <v>112</v>
@@ -9614,10 +9623,10 @@
         <v>114</v>
       </c>
       <c r="H9" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="I9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="J9" t="s">
         <v>335</v>
@@ -9632,7 +9641,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O9" t="s">
         <v>417</v>
@@ -9643,13 +9652,13 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C10">
         <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E10" t="s">
         <v>182</v>
@@ -9661,10 +9670,10 @@
         <v>114</v>
       </c>
       <c r="H10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I10" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="J10" t="s">
         <v>335</v>
@@ -9679,7 +9688,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="O10" t="s">
         <v>417</v>
@@ -9690,13 +9699,13 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C11">
         <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E11" t="s">
         <v>251</v>
@@ -9708,10 +9717,10 @@
         <v>114</v>
       </c>
       <c r="H11" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I11" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="J11" t="s">
         <v>335</v>
@@ -9726,7 +9735,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="O11" t="s">
         <v>417</v>

--- a/05_metadata/AI_质检实验题库_实验一实验二_多目标采购版.xlsx
+++ b/05_metadata/AI_质检实验题库_实验一实验二_多目标采购版.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\streamlit_mvtec_experiment\05_metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0557A934-BC4C-44DD-8A27-D1C52CA5F27A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D4D625-0EB5-4AB9-8D29-EFE8317CA29E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1662" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1662" uniqueCount="510">
   <si>
     <t>AI辅助质检实验题库（实验一 + 实验二多目标采购版）</t>
   </si>
@@ -521,9 +521,6 @@
     <t>BOT_NG_H02</t>
   </si>
   <si>
-    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw\bottle\ground_truth\broken_small\000_mask.png</t>
-  </si>
-  <si>
     <t>bottle/test/broken_small/000.png</t>
   </si>
   <si>
@@ -596,9 +593,6 @@
     <t>系统在左侧检测到裂缝，胶囊表面与正常模板相比存在可分辨差异，异常区域约占图像2.33%。综合异常位置、面积与形态特征，判定为不合格。</t>
   </si>
   <si>
-    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw\capsule\ground_truth\crack\001_mask.png</t>
-  </si>
-  <si>
     <t>capsule/test/crack/001.png</t>
   </si>
   <si>
@@ -611,9 +605,6 @@
     <t>系统在中心区域检测到裂缝，胶囊表面与正常模板相比存在可分辨差异，异常区域约占图像1.80%。综合异常位置、面积与形态特征，判定为不合格。</t>
   </si>
   <si>
-    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw\capsule\ground_truth\crack\010_mask.png</t>
-  </si>
-  <si>
     <t>capsule/test/crack/010.png</t>
   </si>
   <si>
@@ -623,9 +614,6 @@
     <t>挤压变形</t>
   </si>
   <si>
-    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw\capsule\ground_truth\squeeze\007_mask.png</t>
-  </si>
-  <si>
     <t>capsule/test/squeeze/007.png</t>
   </si>
   <si>
@@ -644,9 +632,6 @@
     <t>系统在右侧检测到针孔，胶囊表面与正常模板相比存在可分辨差异，异常区域约占图像1.23%。综合异常位置、面积与形态特征，判定为不合格。</t>
   </si>
   <si>
-    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw\capsule\ground_truth\poke\000_mask.png</t>
-  </si>
-  <si>
     <t>capsule/test/poke/000.png</t>
   </si>
   <si>
@@ -686,9 +671,6 @@
     <t>系统在中心区域检测到针孔，胶囊表面与正常模板相比存在可分辨差异，异常区域约占图像0.16%。综合异常位置、面积与形态特征，判定为不合格。</t>
   </si>
   <si>
-    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw\capsule\ground_truth\poke\006_mask.png</t>
-  </si>
-  <si>
     <t>capsule/test/poke/006.png</t>
   </si>
   <si>
@@ -701,9 +683,6 @@
     <t>系统在右侧检测到针孔，胶囊表面与正常模板相比存在可分辨差异，异常区域约占图像0.29%。综合异常位置、面积与形态特征，判定为不合格。</t>
   </si>
   <si>
-    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw\capsule\ground_truth\poke\012_mask.png</t>
-  </si>
-  <si>
     <t>capsule/test/poke/012.png</t>
   </si>
   <si>
@@ -713,9 +692,6 @@
     <t>划痕</t>
   </si>
   <si>
-    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw\capsule\ground_truth\scratch\002_mask.png</t>
-  </si>
-  <si>
     <t>capsule/test/scratch/002.png</t>
   </si>
   <si>
@@ -728,9 +704,6 @@
     <t>系统在中心区域检测到划痕，胶囊表面与正常模板相比存在可分辨差异，异常区域约占图像0.30%。综合异常位置、面积与形态特征，判定为不合格。</t>
   </si>
   <si>
-    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw\capsule\ground_truth\scratch\005_mask.png</t>
-  </si>
-  <si>
     <t>capsule/test/scratch/005.png</t>
   </si>
   <si>
@@ -788,9 +761,6 @@
     <t>系统在上部检测到弯曲变形，螺母表面与边缘与正常模板相比存在可分辨差异，异常区域约占图像4.70%。综合异常位置、面积与形态特征，判定为不合格。</t>
   </si>
   <si>
-    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw\metal_nut\ground_truth\bent\000_mask.png</t>
-  </si>
-  <si>
     <t>metal_nut/test/bent/000.png</t>
   </si>
   <si>
@@ -809,18 +779,12 @@
     <t>系统在右侧检测到局部色差，螺母表面与边缘与正常模板相比存在可分辨差异，异常区域约占图像2.28%。综合异常位置、面积与形态特征，判定为不合格。</t>
   </si>
   <si>
-    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw\metal_nut\ground_truth\color\019_mask.png</t>
-  </si>
-  <si>
     <t>metal_nut/test/color/019.png</t>
   </si>
   <si>
     <t>MET_NG_L03</t>
   </si>
   <si>
-    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw\metal_nut\ground_truth\color\011_mask.png</t>
-  </si>
-  <si>
     <t>metal_nut/test/color/011.png</t>
   </si>
   <si>
@@ -833,9 +797,6 @@
     <t>系统在上部右侧检测到局部色差，螺母表面与边缘与正常模板相比存在可分辨差异，异常区域约占图像6.57%。综合异常位置、面积与形态特征，判定为不合格。</t>
   </si>
   <si>
-    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw\metal_nut\ground_truth\color\012_mask.png</t>
-  </si>
-  <si>
     <t>metal_nut/test/color/012.png</t>
   </si>
   <si>
@@ -848,9 +809,6 @@
     <t>系统在下部左侧检测到弯曲变形，螺母表面与边缘与正常模板相比存在可分辨差异，异常区域约占图像2.01%。综合异常位置、面积与形态特征，判定为不合格。</t>
   </si>
   <si>
-    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw\metal_nut\ground_truth\bent\021_mask.png</t>
-  </si>
-  <si>
     <t>metal_nut/test/bent/021.png</t>
   </si>
   <si>
@@ -866,18 +824,12 @@
     <t>系统在下部检测到划痕，螺母表面与边缘与正常模板相比存在可分辨差异，异常区域约占图像7.37%。综合异常位置、面积与形态特征，判定为不合格。</t>
   </si>
   <si>
-    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw\metal_nut\ground_truth\scratch\022_mask.png</t>
-  </si>
-  <si>
     <t>metal_nut/test/scratch/022.png</t>
   </si>
   <si>
     <t>MET_OK_H03</t>
   </si>
   <si>
-    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw\metal_nut\ground_truth\bent\014_mask.png</t>
-  </si>
-  <si>
     <t>metal_nut/test/bent/014.png</t>
   </si>
   <si>
@@ -891,9 +843,6 @@
   </si>
   <si>
     <t>系统在中心区域检测到朝向异常，螺母表面与边缘与正常模板相比存在可分辨差异，异常区域约占图像48.16%。综合异常位置、面积与形态特征，判定为不合格。</t>
-  </si>
-  <si>
-    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw\metal_nut\ground_truth\flip\022_mask.png</t>
   </si>
   <si>
     <t>metal_nut/test/flip/022.png</t>
@@ -1230,18 +1179,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>bottle\test\broken_large\006.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>置信度：92%｜异常面积占比：34.33%｜异常像素：27,013 px｜主异常位置：左上侧｜异常显著性：高</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>bottle\test\broken_large\018.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>系统在中心区域检测到污染/附着异常，瓶体与正常模板相比存在可分辨差异，异常区域约占图像45.69%。综合异常位置、面积与形态特征，判定为不合格。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1254,14 +1195,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>bottle\test\contamination\005.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bottle\test\contamination\011.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>系统检测到左上侧存在破损，瓶体与正常样本存在差异，综合判断为不合格。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1282,34 +1215,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw\bottle\ground_truth\broken_large\006_mask.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw\bottle\ground_truth\broken_large\018_mask.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw\bottle\ground_truth\contamination\005_mask.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw\bottle\ground_truth\contamination\011_mask.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw\bottle\ground_truth\contamination\009_mask.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw\bottle\ground_truth\contamination\019_mask.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw\bottle\ground_truth\broken_small\014_mask.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>置信度：96%｜异常面积占比：73.78%｜异常像素：11,640 px｜主异常位置：中心区域｜异常显著性：高</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1512,6 +1417,223 @@
   <si>
     <t>该胶囊存在“渗漏”相关质量表现，结合供应价格 12.5 元/件进行综合评估。其质量或成本条件不足以支持采购。</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw_compressed_compressed\bottle\ground_truth\broken_large\006_mask.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bottle/test/good/003.jpg</t>
+  </si>
+  <si>
+    <t>bottle/test/good/004.jpg</t>
+  </si>
+  <si>
+    <t>bottle/test/good/007.jpg</t>
+  </si>
+  <si>
+    <t>bottle/test/good/001.jpg</t>
+  </si>
+  <si>
+    <t>bottle\test\broken_large\006.jpg</t>
+  </si>
+  <si>
+    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw_compressed\bottle\ground_truth\broken_large\018_mask.jpg</t>
+  </si>
+  <si>
+    <t>bottle\test\broken_large\018.jpg</t>
+  </si>
+  <si>
+    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw_compressed\bottle\ground_truth\contamination\005_mask.jpg</t>
+  </si>
+  <si>
+    <t>bottle\test\contamination\005.jpg</t>
+  </si>
+  <si>
+    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw_compressed\bottle\ground_truth\contamination\011_mask.jpg</t>
+  </si>
+  <si>
+    <t>bottle\test\contamination\011.jpg</t>
+  </si>
+  <si>
+    <t>bottle/test/good/006.jpg</t>
+  </si>
+  <si>
+    <t>bottle/test/good/011.jpg</t>
+  </si>
+  <si>
+    <t>bottle/test/good/012.jpg</t>
+  </si>
+  <si>
+    <t>bottle/test/good/002.jpg</t>
+  </si>
+  <si>
+    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw_compressed\bottle\ground_truth\broken_small\014_mask.jpg</t>
+  </si>
+  <si>
+    <t>bottle/test/broken_small/014.jpg</t>
+  </si>
+  <si>
+    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw_compressed\bottle\ground_truth\broken_small\000_mask.jpg</t>
+  </si>
+  <si>
+    <t>bottle/test/broken_small/000.jpg</t>
+  </si>
+  <si>
+    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw_compressed\bottle\ground_truth\contamination\009_mask.jpg</t>
+  </si>
+  <si>
+    <t>bottle/test/contamination/009.jpg</t>
+  </si>
+  <si>
+    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw_compressed\bottle\ground_truth\contamination\019_mask.jpg</t>
+  </si>
+  <si>
+    <t>bottle/test/contamination/019.jpg</t>
+  </si>
+  <si>
+    <t>capsule/test/good/001.jpg</t>
+  </si>
+  <si>
+    <t>capsule/test/good/006.jpg</t>
+  </si>
+  <si>
+    <t>capsule/test/good/007.jpg</t>
+  </si>
+  <si>
+    <t>capsule/test/good/020.jpg</t>
+  </si>
+  <si>
+    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw_compressed\capsule\ground_truth\crack\001_mask.jpg</t>
+  </si>
+  <si>
+    <t>capsule/test/crack/001.jpg</t>
+  </si>
+  <si>
+    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw_compressed\capsule\ground_truth\crack\010_mask.jpg</t>
+  </si>
+  <si>
+    <t>capsule/test/crack/010.jpg</t>
+  </si>
+  <si>
+    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw_compressed\capsule\ground_truth\squeeze\007_mask.jpg</t>
+  </si>
+  <si>
+    <t>capsule/test/squeeze/007.jpg</t>
+  </si>
+  <si>
+    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw_compressed\capsule\ground_truth\poke\000_mask.jpg</t>
+  </si>
+  <si>
+    <t>capsule/test/poke/000.jpg</t>
+  </si>
+  <si>
+    <t>capsule/test/good/002.jpg</t>
+  </si>
+  <si>
+    <t>capsule/test/good/005.jpg</t>
+  </si>
+  <si>
+    <t>capsule/test/good/012.jpg</t>
+  </si>
+  <si>
+    <t>capsule/test/good/014.jpg</t>
+  </si>
+  <si>
+    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw_compressed\capsule\ground_truth\poke\006_mask.jpg</t>
+  </si>
+  <si>
+    <t>capsule/test/poke/006.jpg</t>
+  </si>
+  <si>
+    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw_compressed\capsule\ground_truth\poke\012_mask.jpg</t>
+  </si>
+  <si>
+    <t>capsule/test/poke/012.jpg</t>
+  </si>
+  <si>
+    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw_compressed\capsule\ground_truth\scratch\002_mask.jpg</t>
+  </si>
+  <si>
+    <t>capsule/test/scratch/002.jpg</t>
+  </si>
+  <si>
+    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw_compressed\capsule\ground_truth\scratch\005_mask.jpg</t>
+  </si>
+  <si>
+    <t>capsule/test/scratch/005.jpg</t>
+  </si>
+  <si>
+    <t>metal_nut/test/good/004.jpg</t>
+  </si>
+  <si>
+    <t>metal_nut/test/good/009.jpg</t>
+  </si>
+  <si>
+    <t>metal_nut/test/good/016.jpg</t>
+  </si>
+  <si>
+    <t>metal_nut/test/good/020.jpg</t>
+  </si>
+  <si>
+    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw_compressed\metal_nut\ground_truth\bent\000_mask.jpg</t>
+  </si>
+  <si>
+    <t>metal_nut/test/bent/000.jpg</t>
+  </si>
+  <si>
+    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw_compressed\metal_nut\ground_truth\color\019_mask.jpg</t>
+  </si>
+  <si>
+    <t>metal_nut/test/color/019.jpg</t>
+  </si>
+  <si>
+    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw_compressed\metal_nut\ground_truth\color\011_mask.jpg</t>
+  </si>
+  <si>
+    <t>metal_nut/test/color/011.jpg</t>
+  </si>
+  <si>
+    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw_compressed\metal_nut\ground_truth\color\012_mask.jpg</t>
+  </si>
+  <si>
+    <t>metal_nut/test/color/012.jpg</t>
+  </si>
+  <si>
+    <t>metal_nut/test/good/005.jpg</t>
+  </si>
+  <si>
+    <t>metal_nut/test/good/007.jpg</t>
+  </si>
+  <si>
+    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw_compressed\metal_nut\ground_truth\bent\014_mask.jpg</t>
+  </si>
+  <si>
+    <t>metal_nut/test/bent/014.jpg</t>
+  </si>
+  <si>
+    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw_compressed\metal_nut\ground_truth\flip\022_mask.jpg</t>
+  </si>
+  <si>
+    <t>metal_nut/test/flip/022.jpg</t>
+  </si>
+  <si>
+    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw_compressed\metal_nut\ground_truth\bent\021_mask.jpg</t>
+  </si>
+  <si>
+    <t>metal_nut/test/bent/021.jpg</t>
+  </si>
+  <si>
+    <t>D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\00_raw_compressed\metal_nut\ground_truth\scratch\022_mask.jpg</t>
+  </si>
+  <si>
+    <t>metal_nut/test/scratch/022.jpg</t>
+  </si>
+  <si>
+    <t>metal_nut/test/good/008.jpg</t>
+  </si>
+  <si>
+    <t>metal_nut/test/good/012.jpg</t>
   </si>
 </sst>
 </file>
@@ -1554,12 +1676,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2350,8 +2469,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:S51"/>
+  <dimension ref="A1:S49"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="14" max="14" width="28.6328125" bestFit="1" customWidth="1"/>
@@ -2421,7 +2539,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2468,19 +2586,19 @@
         <v>119</v>
       </c>
       <c r="P2" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="Q2" t="s">
-        <v>420</v>
+        <v>392</v>
       </c>
       <c r="R2" t="s">
         <v>121</v>
       </c>
       <c r="S2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2536,10 +2654,10 @@
         <v>121</v>
       </c>
       <c r="S3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2595,10 +2713,10 @@
         <v>121</v>
       </c>
       <c r="S4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2654,10 +2772,10 @@
         <v>121</v>
       </c>
       <c r="S5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2701,22 +2819,22 @@
         <v>118</v>
       </c>
       <c r="O6" t="s">
-        <v>403</v>
+        <v>382</v>
       </c>
       <c r="P6" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="Q6" t="s">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="R6" t="s">
-        <v>408</v>
+        <v>438</v>
       </c>
       <c r="S6" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2760,22 +2878,22 @@
         <v>118</v>
       </c>
       <c r="O7" t="s">
-        <v>404</v>
+        <v>383</v>
       </c>
       <c r="P7" t="s">
-        <v>406</v>
+        <v>385</v>
       </c>
       <c r="Q7" t="s">
-        <v>400</v>
+        <v>381</v>
       </c>
       <c r="R7" t="s">
-        <v>409</v>
+        <v>444</v>
       </c>
       <c r="S7" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2822,19 +2940,19 @@
         <v>119</v>
       </c>
       <c r="P8" t="s">
-        <v>407</v>
+        <v>386</v>
       </c>
       <c r="Q8" t="s">
-        <v>398</v>
+        <v>379</v>
       </c>
       <c r="R8" t="s">
-        <v>410</v>
+        <v>446</v>
       </c>
       <c r="S8" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2887,13 +3005,13 @@
         <v>128</v>
       </c>
       <c r="R9" t="s">
-        <v>411</v>
+        <v>448</v>
       </c>
       <c r="S9" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2940,19 +3058,19 @@
         <v>119</v>
       </c>
       <c r="P10" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q10" t="s">
         <v>393</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>421</v>
       </c>
       <c r="R10" t="s">
         <v>121</v>
       </c>
       <c r="S10" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3008,10 +3126,10 @@
         <v>121</v>
       </c>
       <c r="S11" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3067,10 +3185,10 @@
         <v>121</v>
       </c>
       <c r="S12" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3117,7 +3235,7 @@
         <v>126</v>
       </c>
       <c r="P13" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="Q13" t="s">
         <v>128</v>
@@ -3126,10 +3244,10 @@
         <v>121</v>
       </c>
       <c r="S13" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3176,19 +3294,19 @@
         <v>157</v>
       </c>
       <c r="P14" t="s">
-        <v>417</v>
+        <v>389</v>
       </c>
       <c r="Q14" t="s">
-        <v>416</v>
+        <v>388</v>
       </c>
       <c r="R14" t="s">
-        <v>414</v>
+        <v>454</v>
       </c>
       <c r="S14" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3235,24 +3353,24 @@
         <v>157</v>
       </c>
       <c r="P15" t="s">
-        <v>418</v>
+        <v>390</v>
       </c>
       <c r="Q15" t="s">
-        <v>419</v>
+        <v>391</v>
       </c>
       <c r="R15" t="s">
-        <v>160</v>
+        <v>456</v>
       </c>
       <c r="S15" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C16" t="s">
         <v>110</v>
@@ -3294,24 +3412,24 @@
         <v>119</v>
       </c>
       <c r="P16" t="s">
-        <v>415</v>
+        <v>387</v>
       </c>
       <c r="Q16" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="R16" t="s">
-        <v>412</v>
+        <v>458</v>
       </c>
       <c r="S16" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C17" t="s">
         <v>110</v>
@@ -3353,30 +3471,30 @@
         <v>126</v>
       </c>
       <c r="P17" t="s">
-        <v>405</v>
+        <v>384</v>
       </c>
       <c r="Q17" t="s">
         <v>128</v>
       </c>
       <c r="R17" t="s">
-        <v>413</v>
+        <v>460</v>
       </c>
       <c r="S17" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>166</v>
+      </c>
+      <c r="C18" t="s">
         <v>167</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>168</v>
-      </c>
-      <c r="D18" t="s">
-        <v>169</v>
       </c>
       <c r="E18" t="s">
         <v>112</v>
@@ -3409,33 +3527,33 @@
         <v>118</v>
       </c>
       <c r="O18" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P18" t="s">
-        <v>423</v>
+        <v>395</v>
       </c>
       <c r="Q18" t="s">
-        <v>420</v>
+        <v>392</v>
       </c>
       <c r="R18" t="s">
         <v>121</v>
       </c>
       <c r="S18" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C19" t="s">
+        <v>167</v>
+      </c>
+      <c r="D19" t="s">
         <v>168</v>
-      </c>
-      <c r="D19" t="s">
-        <v>169</v>
       </c>
       <c r="E19" t="s">
         <v>112</v>
@@ -3468,33 +3586,33 @@
         <v>125</v>
       </c>
       <c r="O19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P19" t="s">
         <v>127</v>
       </c>
       <c r="Q19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="R19" t="s">
         <v>121</v>
       </c>
       <c r="S19" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C20" t="s">
+        <v>167</v>
+      </c>
+      <c r="D20" t="s">
         <v>168</v>
-      </c>
-      <c r="D20" t="s">
-        <v>169</v>
       </c>
       <c r="E20" t="s">
         <v>112</v>
@@ -3527,33 +3645,33 @@
         <v>125</v>
       </c>
       <c r="O20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P20" t="s">
         <v>141</v>
       </c>
       <c r="Q20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="R20" t="s">
         <v>121</v>
       </c>
       <c r="S20" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C21" t="s">
+        <v>167</v>
+      </c>
+      <c r="D21" t="s">
         <v>168</v>
-      </c>
-      <c r="D21" t="s">
-        <v>169</v>
       </c>
       <c r="E21" t="s">
         <v>112</v>
@@ -3586,36 +3704,36 @@
         <v>125</v>
       </c>
       <c r="O21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P21" t="s">
         <v>131</v>
       </c>
       <c r="Q21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="R21" t="s">
         <v>121</v>
       </c>
       <c r="S21" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>179</v>
+      </c>
+      <c r="C22" t="s">
+        <v>167</v>
+      </c>
+      <c r="D22" t="s">
+        <v>168</v>
+      </c>
+      <c r="E22" t="s">
         <v>180</v>
-      </c>
-      <c r="C22" t="s">
-        <v>168</v>
-      </c>
-      <c r="D22" t="s">
-        <v>169</v>
-      </c>
-      <c r="E22" t="s">
-        <v>181</v>
       </c>
       <c r="F22" t="s">
         <v>113</v>
@@ -3645,36 +3763,36 @@
         <v>118</v>
       </c>
       <c r="O22" t="s">
+        <v>181</v>
+      </c>
+      <c r="P22" t="s">
         <v>182</v>
       </c>
-      <c r="P22" t="s">
+      <c r="Q22" t="s">
         <v>183</v>
       </c>
-      <c r="Q22" t="s">
-        <v>184</v>
-      </c>
       <c r="R22" t="s">
-        <v>185</v>
+        <v>466</v>
       </c>
       <c r="S22" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C23" t="s">
+        <v>167</v>
+      </c>
+      <c r="D23" t="s">
         <v>168</v>
       </c>
-      <c r="D23" t="s">
-        <v>169</v>
-      </c>
       <c r="E23" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F23" t="s">
         <v>113</v>
@@ -3704,36 +3822,36 @@
         <v>118</v>
       </c>
       <c r="O23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P23" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="Q23" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="R23" t="s">
-        <v>190</v>
+        <v>468</v>
       </c>
       <c r="S23" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C24" t="s">
+        <v>167</v>
+      </c>
+      <c r="D24" t="s">
         <v>168</v>
       </c>
-      <c r="D24" t="s">
-        <v>169</v>
-      </c>
       <c r="E24" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F24" t="s">
         <v>113</v>
@@ -3763,36 +3881,36 @@
         <v>125</v>
       </c>
       <c r="O24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P24" t="s">
-        <v>426</v>
+        <v>398</v>
       </c>
       <c r="Q24" t="s">
-        <v>428</v>
+        <v>400</v>
       </c>
       <c r="R24" t="s">
-        <v>194</v>
+        <v>470</v>
       </c>
       <c r="S24" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C25" t="s">
+        <v>167</v>
+      </c>
+      <c r="D25" t="s">
         <v>168</v>
       </c>
-      <c r="D25" t="s">
-        <v>169</v>
-      </c>
       <c r="E25" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F25" t="s">
         <v>113</v>
@@ -3822,33 +3940,33 @@
         <v>118</v>
       </c>
       <c r="O25" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P25" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="Q25" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="R25" t="s">
-        <v>201</v>
+        <v>472</v>
       </c>
       <c r="S25" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C26" t="s">
+        <v>167</v>
+      </c>
+      <c r="D26" t="s">
         <v>168</v>
-      </c>
-      <c r="D26" t="s">
-        <v>169</v>
       </c>
       <c r="E26" t="s">
         <v>112</v>
@@ -3881,33 +3999,33 @@
         <v>118</v>
       </c>
       <c r="O26" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P26" t="s">
-        <v>424</v>
+        <v>396</v>
       </c>
       <c r="Q26" t="s">
-        <v>425</v>
+        <v>397</v>
       </c>
       <c r="R26" t="s">
         <v>121</v>
       </c>
       <c r="S26" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C27" t="s">
+        <v>167</v>
+      </c>
+      <c r="D27" t="s">
         <v>168</v>
-      </c>
-      <c r="D27" t="s">
-        <v>169</v>
       </c>
       <c r="E27" t="s">
         <v>112</v>
@@ -3940,33 +4058,33 @@
         <v>125</v>
       </c>
       <c r="O27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P27" t="s">
         <v>134</v>
       </c>
       <c r="Q27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="R27" t="s">
         <v>121</v>
       </c>
       <c r="S27" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C28" t="s">
+        <v>167</v>
+      </c>
+      <c r="D28" t="s">
         <v>168</v>
-      </c>
-      <c r="D28" t="s">
-        <v>169</v>
       </c>
       <c r="E28" t="s">
         <v>112</v>
@@ -3999,33 +4117,33 @@
         <v>125</v>
       </c>
       <c r="O28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P28" t="s">
         <v>141</v>
       </c>
       <c r="Q28" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="R28" t="s">
         <v>121</v>
       </c>
       <c r="S28" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C29" t="s">
+        <v>167</v>
+      </c>
+      <c r="D29" t="s">
         <v>168</v>
-      </c>
-      <c r="D29" t="s">
-        <v>169</v>
       </c>
       <c r="E29" t="s">
         <v>112</v>
@@ -4058,36 +4176,36 @@
         <v>125</v>
       </c>
       <c r="O29" t="s">
+        <v>172</v>
+      </c>
+      <c r="P29" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q29" t="s">
         <v>173</v>
-      </c>
-      <c r="P29" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>174</v>
       </c>
       <c r="R29" t="s">
         <v>121</v>
       </c>
       <c r="S29" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C30" t="s">
+        <v>167</v>
+      </c>
+      <c r="D30" t="s">
         <v>168</v>
       </c>
-      <c r="D30" t="s">
-        <v>169</v>
-      </c>
       <c r="E30" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F30" t="s">
         <v>151</v>
@@ -4117,36 +4235,36 @@
         <v>118</v>
       </c>
       <c r="O30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P30" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="Q30" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="R30" t="s">
-        <v>215</v>
+        <v>478</v>
       </c>
       <c r="S30" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C31" t="s">
+        <v>167</v>
+      </c>
+      <c r="D31" t="s">
         <v>168</v>
       </c>
-      <c r="D31" t="s">
-        <v>169</v>
-      </c>
       <c r="E31" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F31" t="s">
         <v>151</v>
@@ -4176,36 +4294,36 @@
         <v>118</v>
       </c>
       <c r="O31" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P31" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="Q31" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="R31" t="s">
-        <v>220</v>
+        <v>480</v>
       </c>
       <c r="S31" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="C32" t="s">
+        <v>167</v>
+      </c>
+      <c r="D32" t="s">
         <v>168</v>
       </c>
-      <c r="D32" t="s">
-        <v>169</v>
-      </c>
       <c r="E32" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F32" t="s">
         <v>151</v>
@@ -4235,36 +4353,36 @@
         <v>125</v>
       </c>
       <c r="O32" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P32" t="s">
-        <v>427</v>
+        <v>399</v>
       </c>
       <c r="Q32" t="s">
-        <v>428</v>
+        <v>400</v>
       </c>
       <c r="R32" t="s">
-        <v>224</v>
+        <v>482</v>
       </c>
       <c r="S32" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C33" t="s">
+        <v>167</v>
+      </c>
+      <c r="D33" t="s">
         <v>168</v>
       </c>
-      <c r="D33" t="s">
-        <v>169</v>
-      </c>
       <c r="E33" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F33" t="s">
         <v>151</v>
@@ -4294,33 +4412,33 @@
         <v>118</v>
       </c>
       <c r="O33" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P33" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="Q33" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="R33" t="s">
-        <v>229</v>
+        <v>484</v>
       </c>
       <c r="S33" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C34" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D34" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E34" t="s">
         <v>112</v>
@@ -4353,33 +4471,33 @@
         <v>125</v>
       </c>
       <c r="O34" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="P34" t="s">
         <v>127</v>
       </c>
       <c r="Q34" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="R34" t="s">
         <v>121</v>
       </c>
       <c r="S34" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C35" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D35" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E35" t="s">
         <v>112</v>
@@ -4412,7 +4530,7 @@
         <v>118</v>
       </c>
       <c r="O35" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="P35" t="s">
         <v>145</v>
@@ -4424,21 +4542,21 @@
         <v>121</v>
       </c>
       <c r="S35" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="C36" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D36" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E36" t="s">
         <v>112</v>
@@ -4471,33 +4589,33 @@
         <v>125</v>
       </c>
       <c r="O36" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="P36" t="s">
         <v>148</v>
       </c>
       <c r="Q36" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="R36" t="s">
         <v>121</v>
       </c>
       <c r="S36" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="C37" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D37" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E37" t="s">
         <v>112</v>
@@ -4530,36 +4648,36 @@
         <v>125</v>
       </c>
       <c r="O37" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="P37" t="s">
         <v>131</v>
       </c>
       <c r="Q37" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="R37" t="s">
         <v>121</v>
       </c>
       <c r="S37" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="C38" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D38" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E38" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="F38" t="s">
         <v>113</v>
@@ -4589,36 +4707,36 @@
         <v>118</v>
       </c>
       <c r="O38" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="P38" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="Q38" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="R38" t="s">
-        <v>249</v>
+        <v>490</v>
       </c>
       <c r="S38" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C39" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D39" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E39" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F39" t="s">
         <v>113</v>
@@ -4648,36 +4766,36 @@
         <v>118</v>
       </c>
       <c r="O39" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="P39" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="Q39" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="R39" t="s">
-        <v>256</v>
+        <v>492</v>
       </c>
       <c r="S39" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="C40" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D40" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E40" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F40" t="s">
         <v>113</v>
@@ -4707,36 +4825,36 @@
         <v>125</v>
       </c>
       <c r="O40" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="P40" t="s">
-        <v>429</v>
+        <v>401</v>
       </c>
       <c r="Q40" t="s">
-        <v>428</v>
+        <v>400</v>
       </c>
       <c r="R40" t="s">
-        <v>259</v>
+        <v>494</v>
       </c>
       <c r="S40" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="C41" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D41" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E41" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F41" t="s">
         <v>113</v>
@@ -4766,19 +4884,19 @@
         <v>118</v>
       </c>
       <c r="O41" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="P41" t="s">
-        <v>430</v>
+        <v>402</v>
       </c>
       <c r="Q41" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="R41" t="s">
-        <v>264</v>
+        <v>496</v>
       </c>
       <c r="S41" t="s">
-        <v>265</v>
+        <v>497</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
@@ -4786,16 +4904,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="C42" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D42" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E42" t="s">
-        <v>422</v>
+        <v>394</v>
       </c>
       <c r="F42" t="s">
         <v>151</v>
@@ -4825,19 +4943,19 @@
         <v>125</v>
       </c>
       <c r="O42" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="P42" t="s">
         <v>131</v>
       </c>
       <c r="Q42" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="R42" t="s">
         <v>121</v>
       </c>
       <c r="S42" t="s">
-        <v>433</v>
+        <v>498</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
@@ -4845,16 +4963,16 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="C43" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D43" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E43" t="s">
-        <v>422</v>
+        <v>394</v>
       </c>
       <c r="F43" t="s">
         <v>151</v>
@@ -4884,19 +5002,19 @@
         <v>125</v>
       </c>
       <c r="O43" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="P43" t="s">
         <v>131</v>
       </c>
       <c r="Q43" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="R43" t="s">
         <v>121</v>
       </c>
       <c r="S43" t="s">
-        <v>434</v>
+        <v>499</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
@@ -4904,16 +5022,16 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D44" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E44" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="F44" t="s">
         <v>151</v>
@@ -4943,19 +5061,19 @@
         <v>118</v>
       </c>
       <c r="O44" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="P44" t="s">
-        <v>431</v>
+        <v>403</v>
       </c>
       <c r="Q44" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="R44" t="s">
-        <v>278</v>
+        <v>500</v>
       </c>
       <c r="S44" t="s">
-        <v>279</v>
+        <v>501</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
@@ -4963,16 +5081,16 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="C45" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D45" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E45" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F45" t="s">
         <v>151</v>
@@ -5002,19 +5120,19 @@
         <v>118</v>
       </c>
       <c r="O45" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="P45" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="Q45" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="R45" t="s">
-        <v>284</v>
+        <v>502</v>
       </c>
       <c r="S45" t="s">
-        <v>285</v>
+        <v>503</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
@@ -5022,16 +5140,16 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="C46" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D46" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E46" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="F46" t="s">
         <v>151</v>
@@ -5061,19 +5179,19 @@
         <v>125</v>
       </c>
       <c r="O46" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="P46" t="s">
-        <v>432</v>
+        <v>404</v>
       </c>
       <c r="Q46" t="s">
-        <v>428</v>
+        <v>400</v>
       </c>
       <c r="R46" t="s">
-        <v>269</v>
+        <v>504</v>
       </c>
       <c r="S46" t="s">
-        <v>270</v>
+        <v>505</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
@@ -5081,16 +5199,16 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="C47" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D47" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E47" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="F47" t="s">
         <v>151</v>
@@ -5120,19 +5238,19 @@
         <v>118</v>
       </c>
       <c r="O47" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="P47" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="Q47" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="R47" t="s">
-        <v>275</v>
+        <v>506</v>
       </c>
       <c r="S47" t="s">
-        <v>276</v>
+        <v>507</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
@@ -5140,16 +5258,16 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="C48" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D48" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E48" t="s">
-        <v>422</v>
+        <v>394</v>
       </c>
       <c r="F48" t="s">
         <v>151</v>
@@ -5179,19 +5297,19 @@
         <v>118</v>
       </c>
       <c r="O48" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="P48" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="Q48" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="R48" t="s">
         <v>121</v>
       </c>
       <c r="S48" t="s">
-        <v>435</v>
+        <v>508</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
@@ -5199,16 +5317,16 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="C49" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D49" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E49" t="s">
-        <v>422</v>
+        <v>394</v>
       </c>
       <c r="F49" t="s">
         <v>151</v>
@@ -5238,36 +5356,23 @@
         <v>125</v>
       </c>
       <c r="O49" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="P49" t="s">
         <v>131</v>
       </c>
       <c r="Q49" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="R49" t="s">
         <v>121</v>
       </c>
       <c r="S49" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="1:19" hidden="1" x14ac:dyDescent="0.25"/>
+        <v>509</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S51" xr:uid="{00000000-0001-0000-0200-000000000000}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="金属螺母"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="5">
-      <filters>
-        <filter val="高复杂"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:S51" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5319,7 +5424,7 @@
         <v>47</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>438</v>
+        <v>410</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>99</v>
@@ -5346,16 +5451,16 @@
         <v>74</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>77</v>
@@ -5364,16 +5469,16 @@
         <v>80</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>84</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>88</v>
@@ -5382,7 +5487,7 @@
         <v>95</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>106</v>
@@ -5456,16 +5561,16 @@
         <v>采购</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U2" s="1">
         <v>1</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="X2" s="1">
         <v>1</v>
@@ -5474,13 +5579,13 @@
         <v>124</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
@@ -5545,16 +5650,16 @@
         <v>采购</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U3" s="1">
         <v>1</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="X3" s="1">
         <v>1</v>
@@ -5563,13 +5668,13 @@
         <v>124</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
@@ -5634,16 +5739,16 @@
         <v>采购</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="U4" s="1">
         <v>1</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="X4" s="1">
         <v>1</v>
@@ -5652,13 +5757,13 @@
         <v>124</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
@@ -5723,16 +5828,16 @@
         <v>不采购</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U5" s="1">
         <v>0</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="X5" s="1">
         <v>1</v>
@@ -5741,13 +5846,13 @@
         <v>124</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="AA5" s="1" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
@@ -5812,16 +5917,16 @@
         <v>不采购</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U6" s="1">
         <v>0</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="X6" s="1">
         <v>1</v>
@@ -5830,13 +5935,13 @@
         <v>124</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>439</v>
+        <v>411</v>
       </c>
       <c r="AA6" s="1" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
@@ -5901,16 +6006,16 @@
         <v>采购</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="U7" s="1">
         <v>1</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="X7" s="1">
         <v>1</v>
@@ -5919,13 +6024,13 @@
         <v>124</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>441</v>
+        <v>413</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
@@ -5990,31 +6095,31 @@
         <v>采购</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U8" s="1">
         <v>1</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>459</v>
+        <v>431</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="X8" s="1">
         <v>1</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>456</v>
+        <v>428</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>461</v>
+        <v>433</v>
       </c>
       <c r="AA8" s="1" t="s">
-        <v>463</v>
+        <v>435</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
@@ -6079,16 +6184,16 @@
         <v>不采购</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U9" s="1">
         <v>0</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="X9" s="1">
         <v>1</v>
@@ -6097,13 +6202,13 @@
         <v>124</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>440</v>
+        <v>412</v>
       </c>
       <c r="AA9" s="1" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="AB9" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
@@ -6168,16 +6273,16 @@
         <v>采购</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U10" s="1">
         <v>1</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="X10" s="1">
         <v>1</v>
@@ -6186,13 +6291,13 @@
         <v>124</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
       <c r="AA10" s="1" t="s">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="AB10" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
@@ -6257,16 +6362,16 @@
         <v>不采购</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="U11" s="1">
         <v>0</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="X11" s="1">
         <v>1</v>
@@ -6275,13 +6380,13 @@
         <v>124</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
       <c r="AA11" s="1" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="AB11" s="1" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
@@ -6346,16 +6451,16 @@
         <v>不采购</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U12" s="1">
         <v>0</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="X12" s="1">
         <v>1</v>
@@ -6364,13 +6469,13 @@
         <v>124</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="AA12" s="1" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="AB12" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
@@ -6435,16 +6540,16 @@
         <v>不采购</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U13" s="1">
         <v>0</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="X13" s="1">
         <v>1</v>
@@ -6453,13 +6558,13 @@
         <v>124</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="AA13" s="1" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="AB13" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
@@ -6524,16 +6629,16 @@
         <v>不采购</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="U14" s="1">
         <v>1</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="X14" s="1">
         <v>0</v>
@@ -6542,13 +6647,13 @@
         <v>117</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>460</v>
+        <v>432</v>
       </c>
       <c r="AA14" s="1" t="s">
-        <v>462</v>
+        <v>434</v>
       </c>
       <c r="AB14" s="1" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.25">
@@ -6574,7 +6679,7 @@
         <v>152</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I15" s="1">
         <v>61</v>
@@ -6613,16 +6718,16 @@
         <v>不采购</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="U15" s="1">
         <v>0</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="X15" s="1">
         <v>1</v>
@@ -6631,13 +6736,13 @@
         <v>124</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="AA15" s="1" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="AB15" s="1" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
@@ -6645,7 +6750,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>110</v>
@@ -6663,7 +6768,7 @@
         <v>152</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I16" s="1">
         <v>57</v>
@@ -6702,16 +6807,16 @@
         <v>不采购</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="U16" s="1">
         <v>1</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="X16" s="1">
         <v>0</v>
@@ -6720,13 +6825,13 @@
         <v>117</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="AA16" s="1" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="AB16" s="1" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
@@ -6734,7 +6839,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>110</v>
@@ -6752,7 +6857,7 @@
         <v>152</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I17" s="1">
         <v>54</v>
@@ -6791,16 +6896,16 @@
         <v>不采购</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U17" s="1">
         <v>0</v>
       </c>
       <c r="V17" s="1" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="X17" s="1">
         <v>1</v>
@@ -6809,13 +6914,13 @@
         <v>124</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="AA17" s="1" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="AB17" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.25">
@@ -6823,13 +6928,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>112</v>
@@ -6841,7 +6946,7 @@
         <v>114</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I18" s="1">
         <v>92</v>
@@ -6880,16 +6985,16 @@
         <v>采购</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U18" s="1">
         <v>1</v>
       </c>
       <c r="V18" s="1" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="X18" s="1">
         <v>1</v>
@@ -6898,13 +7003,13 @@
         <v>124</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="AA18" s="1" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="AB18" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.25">
@@ -6912,13 +7017,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C19" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>112</v>
@@ -6930,7 +7035,7 @@
         <v>114</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I19" s="1">
         <v>85</v>
@@ -6969,16 +7074,16 @@
         <v>采购</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U19" s="1">
         <v>1</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="X19" s="1">
         <v>1</v>
@@ -6987,13 +7092,13 @@
         <v>124</v>
       </c>
       <c r="Z19" s="1" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="AA19" s="1" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="AB19" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
@@ -7001,13 +7106,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>112</v>
@@ -7019,7 +7124,7 @@
         <v>114</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I20" s="1">
         <v>78</v>
@@ -7058,16 +7163,16 @@
         <v>采购</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="U20" s="1">
         <v>1</v>
       </c>
       <c r="V20" s="1" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="X20" s="1">
         <v>1</v>
@@ -7076,13 +7181,13 @@
         <v>124</v>
       </c>
       <c r="Z20" s="1" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="AA20" s="1" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="AB20" s="1" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
@@ -7090,13 +7195,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>112</v>
@@ -7108,7 +7213,7 @@
         <v>114</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I21" s="1">
         <v>72</v>
@@ -7147,16 +7252,16 @@
         <v>不采购</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U21" s="1">
         <v>0</v>
       </c>
       <c r="V21" s="1" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="X21" s="1">
         <v>1</v>
@@ -7165,13 +7270,13 @@
         <v>124</v>
       </c>
       <c r="Z21" s="1" t="s">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="AA21" s="1" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="AB21" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.25">
@@ -7179,16 +7284,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>181</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>113</v>
@@ -7197,7 +7302,7 @@
         <v>114</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I22" s="1">
         <v>66</v>
@@ -7236,16 +7341,16 @@
         <v>不采购</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U22" s="1">
         <v>0</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="X22" s="1">
         <v>1</v>
@@ -7254,13 +7359,13 @@
         <v>124</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="AA22" s="1" t="s">
-        <v>464</v>
+        <v>436</v>
       </c>
       <c r="AB22" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.25">
@@ -7268,16 +7373,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C23" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="E23" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>113</v>
@@ -7286,7 +7391,7 @@
         <v>114</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I23" s="1">
         <v>59</v>
@@ -7325,31 +7430,31 @@
         <v>不采购</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="U23" s="1">
         <v>0</v>
       </c>
       <c r="V23" s="1" t="s">
-        <v>457</v>
+        <v>429</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="X23" s="1">
         <v>1</v>
       </c>
       <c r="Y23" s="1" t="s">
-        <v>456</v>
+        <v>428</v>
       </c>
       <c r="Z23" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="AA23" s="2" t="s">
-        <v>465</v>
+        <v>430</v>
+      </c>
+      <c r="AA23" s="1" t="s">
+        <v>437</v>
       </c>
       <c r="AB23" s="1" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.25">
@@ -7357,16 +7462,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="E24" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>113</v>
@@ -7375,7 +7480,7 @@
         <v>114</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="I24" s="1">
         <v>52</v>
@@ -7414,16 +7519,16 @@
         <v>不采购</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U24" s="1">
         <v>0</v>
       </c>
       <c r="V24" s="1" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="X24" s="1">
         <v>1</v>
@@ -7432,13 +7537,13 @@
         <v>124</v>
       </c>
       <c r="Z24" s="1" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
       <c r="AA24" s="1" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="AB24" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.25">
@@ -7446,16 +7551,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="E25" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>113</v>
@@ -7464,7 +7569,7 @@
         <v>114</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="I25" s="1">
         <v>44</v>
@@ -7503,16 +7608,16 @@
         <v>不采购</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U25" s="1">
         <v>0</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="X25" s="1">
         <v>1</v>
@@ -7521,13 +7626,13 @@
         <v>124</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
       <c r="AA25" s="1" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="AB25" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="26" spans="1:28" x14ac:dyDescent="0.25">
@@ -7535,13 +7640,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>112</v>
@@ -7553,7 +7658,7 @@
         <v>152</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="I26" s="1">
         <v>83</v>
@@ -7592,16 +7697,16 @@
         <v>采购</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U26" s="1">
         <v>1</v>
       </c>
       <c r="V26" s="1" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="X26" s="1">
         <v>1</v>
@@ -7610,13 +7715,13 @@
         <v>124</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
       <c r="AA26" s="1" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="AB26" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.25">
@@ -7624,13 +7729,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>112</v>
@@ -7642,7 +7747,7 @@
         <v>152</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="I27" s="1">
         <v>76</v>
@@ -7681,16 +7786,16 @@
         <v>不采购</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="U27" s="1">
         <v>0</v>
       </c>
       <c r="V27" s="1" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="X27" s="1">
         <v>1</v>
@@ -7699,13 +7804,13 @@
         <v>124</v>
       </c>
       <c r="Z27" s="1" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
       <c r="AA27" s="1" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="AB27" s="1" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.25">
@@ -7713,13 +7818,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>112</v>
@@ -7731,7 +7836,7 @@
         <v>152</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="I28" s="1">
         <v>71</v>
@@ -7770,16 +7875,16 @@
         <v>不采购</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U28" s="1">
         <v>0</v>
       </c>
       <c r="V28" s="1" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="X28" s="1">
         <v>1</v>
@@ -7788,13 +7893,13 @@
         <v>124</v>
       </c>
       <c r="Z28" s="1" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="AA28" s="1" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="AB28" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.25">
@@ -7802,13 +7907,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C29" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>112</v>
@@ -7820,7 +7925,7 @@
         <v>152</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="I29" s="1">
         <v>68</v>
@@ -7859,16 +7964,16 @@
         <v>不采购</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U29" s="1">
         <v>0</v>
       </c>
       <c r="V29" s="1" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="X29" s="1">
         <v>1</v>
@@ -7877,13 +7982,13 @@
         <v>124</v>
       </c>
       <c r="Z29" s="1" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="AA29" s="1" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="AB29" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="30" spans="1:28" x14ac:dyDescent="0.25">
@@ -7891,16 +7996,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C30" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="E30" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>151</v>
@@ -7909,7 +8014,7 @@
         <v>152</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="I30" s="1">
         <v>63</v>
@@ -7948,16 +8053,16 @@
         <v>不采购</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="U30" s="1">
         <v>1</v>
       </c>
       <c r="V30" s="1" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="X30" s="1">
         <v>0</v>
@@ -7966,13 +8071,13 @@
         <v>117</v>
       </c>
       <c r="Z30" s="1" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="AA30" s="1" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="AB30" s="1" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:28" x14ac:dyDescent="0.25">
@@ -7980,16 +8085,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="E31" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>151</v>
@@ -7998,7 +8103,7 @@
         <v>152</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="I31" s="1">
         <v>61</v>
@@ -8037,16 +8142,16 @@
         <v>不采购</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="U31" s="1">
         <v>0</v>
       </c>
       <c r="V31" s="1" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="X31" s="1">
         <v>1</v>
@@ -8055,13 +8160,13 @@
         <v>124</v>
       </c>
       <c r="Z31" s="1" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="AA31" s="1" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="AB31" s="1" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.25">
@@ -8069,16 +8174,16 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="C32" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="E32" s="1" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>151</v>
@@ -8087,7 +8192,7 @@
         <v>152</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="I32" s="1">
         <v>57</v>
@@ -8126,16 +8231,16 @@
         <v>不采购</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="U32" s="1">
         <v>1</v>
       </c>
       <c r="V32" s="1" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="W32" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="X32" s="1">
         <v>0</v>
@@ -8144,13 +8249,13 @@
         <v>117</v>
       </c>
       <c r="Z32" s="1" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="AA32" s="1" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="AB32" s="1" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" spans="1:28" x14ac:dyDescent="0.25">
@@ -8158,16 +8263,16 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C33" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="D33" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="E33" s="1" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>151</v>
@@ -8176,7 +8281,7 @@
         <v>152</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="I33" s="1">
         <v>54</v>
@@ -8215,16 +8320,16 @@
         <v>不采购</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U33" s="1">
         <v>0</v>
       </c>
       <c r="V33" s="1" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="X33" s="1">
         <v>1</v>
@@ -8233,13 +8338,13 @@
         <v>124</v>
       </c>
       <c r="Z33" s="1" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="AA33" s="1" t="s">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="AB33" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="34" spans="1:28" x14ac:dyDescent="0.25">
@@ -8247,13 +8352,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>112</v>
@@ -8265,7 +8370,7 @@
         <v>114</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="I34" s="1">
         <v>92</v>
@@ -8304,16 +8409,16 @@
         <v>采购</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U34" s="1">
         <v>1</v>
       </c>
       <c r="V34" s="1" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="X34" s="1">
         <v>1</v>
@@ -8322,13 +8427,13 @@
         <v>124</v>
       </c>
       <c r="Z34" s="1" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="AA34" s="1" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="AB34" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="35" spans="1:28" x14ac:dyDescent="0.25">
@@ -8336,13 +8441,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>112</v>
@@ -8354,7 +8459,7 @@
         <v>114</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="I35" s="1">
         <v>85</v>
@@ -8393,16 +8498,16 @@
         <v>采购</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U35" s="1">
         <v>1</v>
       </c>
       <c r="V35" s="1" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="X35" s="1">
         <v>1</v>
@@ -8411,13 +8516,13 @@
         <v>124</v>
       </c>
       <c r="Z35" s="1" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="AA35" s="1" t="s">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="AB35" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="36" spans="1:28" x14ac:dyDescent="0.25">
@@ -8425,13 +8530,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>112</v>
@@ -8443,7 +8548,7 @@
         <v>114</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="I36" s="1">
         <v>78</v>
@@ -8482,16 +8587,16 @@
         <v>采购</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="U36" s="1">
         <v>1</v>
       </c>
       <c r="V36" s="1" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="X36" s="1">
         <v>1</v>
@@ -8500,13 +8605,13 @@
         <v>124</v>
       </c>
       <c r="Z36" s="1" t="s">
-        <v>442</v>
+        <v>414</v>
       </c>
       <c r="AA36" s="1" t="s">
-        <v>444</v>
+        <v>416</v>
       </c>
       <c r="AB36" s="1" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
     </row>
     <row r="37" spans="1:28" x14ac:dyDescent="0.25">
@@ -8514,13 +8619,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>112</v>
@@ -8532,7 +8637,7 @@
         <v>114</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="I37" s="1">
         <v>72</v>
@@ -8571,16 +8676,16 @@
         <v>不采购</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U37" s="1">
         <v>0</v>
       </c>
       <c r="V37" s="1" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="W37" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="X37" s="1">
         <v>1</v>
@@ -8589,13 +8694,13 @@
         <v>124</v>
       </c>
       <c r="Z37" s="1" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="AA37" s="1" t="s">
-        <v>351</v>
+        <v>334</v>
       </c>
       <c r="AB37" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="38" spans="1:28" x14ac:dyDescent="0.25">
@@ -8603,16 +8708,16 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>113</v>
@@ -8621,7 +8726,7 @@
         <v>114</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="I38" s="1">
         <v>66</v>
@@ -8660,16 +8765,16 @@
         <v>不采购</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U38" s="1">
         <v>0</v>
       </c>
       <c r="V38" s="1" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="W38" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="X38" s="1">
         <v>1</v>
@@ -8678,13 +8783,13 @@
         <v>124</v>
       </c>
       <c r="Z38" s="1" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="AA38" s="1" t="s">
-        <v>451</v>
+        <v>423</v>
       </c>
       <c r="AB38" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="39" spans="1:28" x14ac:dyDescent="0.25">
@@ -8692,16 +8797,16 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>113</v>
@@ -8710,7 +8815,7 @@
         <v>114</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="I39" s="1">
         <v>59</v>
@@ -8749,16 +8854,16 @@
         <v>不采购</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="U39" s="1">
         <v>0</v>
       </c>
       <c r="V39" s="1" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="W39" s="1" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="X39" s="1">
         <v>1</v>
@@ -8767,13 +8872,13 @@
         <v>124</v>
       </c>
       <c r="Z39" s="1" t="s">
-        <v>447</v>
+        <v>419</v>
       </c>
       <c r="AA39" s="1" t="s">
-        <v>452</v>
+        <v>424</v>
       </c>
       <c r="AB39" s="1" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
     </row>
     <row r="40" spans="1:28" x14ac:dyDescent="0.25">
@@ -8781,16 +8886,16 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>113</v>
@@ -8799,7 +8904,7 @@
         <v>114</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="I40" s="1">
         <v>52</v>
@@ -8838,16 +8943,16 @@
         <v>不采购</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U40" s="1">
         <v>0</v>
       </c>
       <c r="V40" s="1" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="W40" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="X40" s="1">
         <v>1</v>
@@ -8856,13 +8961,13 @@
         <v>124</v>
       </c>
       <c r="Z40" s="1" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="AA40" s="1" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="AB40" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="41" spans="1:28" x14ac:dyDescent="0.25">
@@ -8870,16 +8975,16 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>113</v>
@@ -8888,7 +8993,7 @@
         <v>114</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="I41" s="1">
         <v>44</v>
@@ -8927,16 +9032,16 @@
         <v>不采购</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U41" s="1">
         <v>0</v>
       </c>
       <c r="V41" s="1" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="W41" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="X41" s="1">
         <v>1</v>
@@ -8945,13 +9050,13 @@
         <v>124</v>
       </c>
       <c r="Z41" s="1" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
       <c r="AA41" s="1" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="AB41" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="42" spans="1:28" x14ac:dyDescent="0.25">
@@ -8959,16 +9064,16 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E42" t="s">
-        <v>422</v>
+        <v>394</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>151</v>
@@ -8977,7 +9082,7 @@
         <v>152</v>
       </c>
       <c r="H42" t="s">
-        <v>433</v>
+        <v>405</v>
       </c>
       <c r="I42" s="1">
         <v>83</v>
@@ -9016,16 +9121,16 @@
         <v>采购</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U42" s="1">
         <v>0</v>
       </c>
       <c r="V42" s="1" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="W42" s="1" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="X42" s="1">
         <v>0</v>
@@ -9034,13 +9139,13 @@
         <v>117</v>
       </c>
       <c r="Z42" s="1" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="AA42" s="1" t="s">
-        <v>445</v>
+        <v>417</v>
       </c>
       <c r="AB42" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="43" spans="1:28" x14ac:dyDescent="0.25">
@@ -9048,16 +9153,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E43" t="s">
-        <v>422</v>
+        <v>394</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>151</v>
@@ -9066,7 +9171,7 @@
         <v>152</v>
       </c>
       <c r="H43" t="s">
-        <v>434</v>
+        <v>406</v>
       </c>
       <c r="I43" s="1">
         <v>76</v>
@@ -9105,16 +9210,16 @@
         <v>不采购</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="U43" s="1">
         <v>0</v>
       </c>
       <c r="V43" s="1" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="W43" s="1" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="X43" s="1">
         <v>1</v>
@@ -9123,13 +9228,13 @@
         <v>124</v>
       </c>
       <c r="Z43" s="1" t="s">
-        <v>443</v>
+        <v>415</v>
       </c>
       <c r="AA43" s="1" t="s">
-        <v>446</v>
+        <v>418</v>
       </c>
       <c r="AB43" s="1" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
     </row>
     <row r="44" spans="1:28" x14ac:dyDescent="0.25">
@@ -9137,16 +9242,16 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E44" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>151</v>
@@ -9155,7 +9260,7 @@
         <v>152</v>
       </c>
       <c r="H44" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="I44" s="1">
         <v>71</v>
@@ -9194,16 +9299,16 @@
         <v>不采购</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U44" s="1">
         <v>0</v>
       </c>
       <c r="V44" s="1" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="W44" s="1" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="X44" s="1">
         <v>1</v>
@@ -9212,13 +9317,13 @@
         <v>124</v>
       </c>
       <c r="Z44" s="1" t="s">
-        <v>448</v>
+        <v>420</v>
       </c>
       <c r="AA44" s="1" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="AB44" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="45" spans="1:28" x14ac:dyDescent="0.25">
@@ -9226,16 +9331,16 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E45" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>151</v>
@@ -9244,7 +9349,7 @@
         <v>152</v>
       </c>
       <c r="H45" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="I45" s="1">
         <v>68</v>
@@ -9283,16 +9388,16 @@
         <v>不采购</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U45" s="1">
         <v>0</v>
       </c>
       <c r="V45" s="1" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="W45" s="1" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="X45" s="1">
         <v>1</v>
@@ -9301,13 +9406,13 @@
         <v>124</v>
       </c>
       <c r="Z45" s="1" t="s">
-        <v>449</v>
+        <v>421</v>
       </c>
       <c r="AA45" s="1" t="s">
-        <v>454</v>
+        <v>426</v>
       </c>
       <c r="AB45" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="46" spans="1:28" x14ac:dyDescent="0.25">
@@ -9315,16 +9420,16 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E46" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>151</v>
@@ -9333,7 +9438,7 @@
         <v>152</v>
       </c>
       <c r="H46" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="I46" s="1">
         <v>63</v>
@@ -9372,16 +9477,16 @@
         <v>不采购</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="U46" s="1">
         <v>0</v>
       </c>
       <c r="V46" s="1" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="W46" s="1" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="X46" s="1">
         <v>1</v>
@@ -9390,13 +9495,13 @@
         <v>124</v>
       </c>
       <c r="Z46" s="1" t="s">
-        <v>450</v>
+        <v>422</v>
       </c>
       <c r="AA46" s="1" t="s">
-        <v>455</v>
+        <v>427</v>
       </c>
       <c r="AB46" s="1" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
     </row>
     <row r="47" spans="1:28" x14ac:dyDescent="0.25">
@@ -9404,16 +9509,16 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E47" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>151</v>
@@ -9422,7 +9527,7 @@
         <v>152</v>
       </c>
       <c r="H47" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="I47" s="1">
         <v>61</v>
@@ -9461,16 +9566,16 @@
         <v>不采购</v>
       </c>
       <c r="T47" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="U47" s="1">
         <v>1</v>
       </c>
       <c r="V47" s="1" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="W47" s="1" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="X47" s="1">
         <v>0</v>
@@ -9479,13 +9584,13 @@
         <v>117</v>
       </c>
       <c r="Z47" s="1" t="s">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="AA47" s="1" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="AB47" s="1" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
     </row>
     <row r="48" spans="1:28" x14ac:dyDescent="0.25">
@@ -9493,16 +9598,16 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E48" t="s">
-        <v>422</v>
+        <v>394</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>151</v>
@@ -9511,7 +9616,7 @@
         <v>152</v>
       </c>
       <c r="H48" t="s">
-        <v>435</v>
+        <v>407</v>
       </c>
       <c r="I48" s="1">
         <v>57</v>
@@ -9550,16 +9655,16 @@
         <v>不采购</v>
       </c>
       <c r="T48" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="U48" s="1">
         <v>1</v>
       </c>
       <c r="V48" s="1" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="W48" s="1" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="X48" s="1">
         <v>0</v>
@@ -9568,13 +9673,13 @@
         <v>117</v>
       </c>
       <c r="Z48" s="1" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="AA48" s="1" t="s">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="AB48" s="1" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
     </row>
     <row r="49" spans="1:28" x14ac:dyDescent="0.25">
@@ -9582,16 +9687,16 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E49" t="s">
-        <v>422</v>
+        <v>394</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>151</v>
@@ -9600,7 +9705,7 @@
         <v>152</v>
       </c>
       <c r="H49" t="s">
-        <v>436</v>
+        <v>408</v>
       </c>
       <c r="I49" s="1">
         <v>54</v>
@@ -9639,16 +9744,16 @@
         <v>不采购</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="U49" s="1">
         <v>1</v>
       </c>
       <c r="V49" s="1" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="W49" s="1" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="X49" s="1">
         <v>0</v>
@@ -9657,13 +9762,13 @@
         <v>117</v>
       </c>
       <c r="Z49" s="1" t="s">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="AA49" s="1" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="AB49" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -9685,15 +9790,15 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="B3" t="s">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="C3" t="s">
         <v>39</v>
@@ -9711,13 +9816,13 @@
         <v>44</v>
       </c>
       <c r="H3" t="s">
-        <v>365</v>
+        <v>348</v>
       </c>
       <c r="I3" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
       <c r="J3" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="K3" t="s">
         <v>102</v>
@@ -9726,7 +9831,7 @@
         <v>60</v>
       </c>
       <c r="M3" t="s">
-        <v>368</v>
+        <v>351</v>
       </c>
       <c r="N3" t="s">
         <v>11</v>
@@ -9737,7 +9842,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>369</v>
+        <v>352</v>
       </c>
       <c r="C4" t="s">
         <v>109</v>
@@ -9752,10 +9857,10 @@
         <v>113</v>
       </c>
       <c r="G4" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
       <c r="H4" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="I4" t="s">
         <v>115</v>
@@ -9770,10 +9875,10 @@
         <v>1</v>
       </c>
       <c r="M4" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="N4" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -9781,7 +9886,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>369</v>
+        <v>352</v>
       </c>
       <c r="C5" t="s">
         <v>147</v>
@@ -9796,10 +9901,10 @@
         <v>113</v>
       </c>
       <c r="G5" t="s">
-        <v>374</v>
+        <v>357</v>
       </c>
       <c r="H5" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="I5" t="s">
         <v>116</v>
@@ -9814,10 +9919,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="s">
-        <v>391</v>
+        <v>374</v>
       </c>
       <c r="N5" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -9825,13 +9930,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>369</v>
+        <v>352</v>
       </c>
       <c r="C6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E6" t="s">
         <v>112</v>
@@ -9840,10 +9945,10 @@
         <v>113</v>
       </c>
       <c r="G6" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="H6" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="I6" t="s">
         <v>115</v>
@@ -9858,10 +9963,10 @@
         <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
       <c r="N6" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -9869,25 +9974,25 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>369</v>
+        <v>352</v>
       </c>
       <c r="C7" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="D7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E7" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F7" t="s">
         <v>151</v>
       </c>
       <c r="G7" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="H7" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="I7" t="s">
         <v>116</v>
@@ -9902,10 +10007,10 @@
         <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
       <c r="N7" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -9913,10 +10018,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="C8" t="s">
-        <v>379</v>
+        <v>362</v>
       </c>
       <c r="D8" t="s">
         <v>111</v>
@@ -9928,28 +10033,28 @@
         <v>113</v>
       </c>
       <c r="G8" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="H8" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="I8" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="J8">
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="L8">
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>382</v>
+        <v>365</v>
       </c>
       <c r="N8" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -9957,10 +10062,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="C9" t="s">
-        <v>383</v>
+        <v>366</v>
       </c>
       <c r="D9" t="s">
         <v>111</v>
@@ -9972,28 +10077,28 @@
         <v>113</v>
       </c>
       <c r="G9" t="s">
-        <v>384</v>
+        <v>367</v>
       </c>
       <c r="H9" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="I9" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
       <c r="N9" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -10001,43 +10106,43 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="C10" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="D10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F10" t="s">
         <v>113</v>
       </c>
       <c r="G10" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="H10" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="I10" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="N10" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -10045,43 +10150,43 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="C11" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="D11" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E11" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F11" t="s">
         <v>113</v>
       </c>
       <c r="G11" t="s">
-        <v>390</v>
+        <v>373</v>
       </c>
       <c r="H11" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="I11" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11" t="s">
-        <v>437</v>
+        <v>409</v>
       </c>
       <c r="N11" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>

--- a/05_metadata/AI_质检实验题库_实验一实验二_多目标采购版.xlsx
+++ b/05_metadata/AI_质检实验题库_实验一实验二_多目标采购版.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\学习资料\大四\毕业论文\MVTec_AD_Thesis\streamlit_mvtec_experiment\05_metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D4D625-0EB5-4AB9-8D29-EFE8317CA29E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF62644-7EBB-4A8B-8497-D4052DDCC016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1662" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1662" uniqueCount="466">
   <si>
     <t>AI辅助质检实验题库（实验一 + 实验二多目标采购版）</t>
   </si>
@@ -407,9 +407,6 @@
     <t>（无缺陷，ground_truth不适用）</t>
   </si>
   <si>
-    <t>bottle/test/good/003.png</t>
-  </si>
-  <si>
     <t>BOT_OK_L02</t>
   </si>
   <si>
@@ -428,36 +425,24 @@
     <t>系统未检测到稳定且连续的异常区域，瓶体整体轮廓、纹理或表面状态处于可接受波动范围内，因此判定为合格。</t>
   </si>
   <si>
-    <t>bottle/test/good/004.png</t>
-  </si>
-  <si>
     <t>BOT_OK_L03</t>
   </si>
   <si>
     <t>置信度：88%｜异常面积占比：0.00%｜异常像素：0 px｜整体一致性：高｜判定位置：全局扫描</t>
   </si>
   <si>
-    <t>bottle/test/good/007.png</t>
-  </si>
-  <si>
     <t>BOT_OK_L04</t>
   </si>
   <si>
     <t>置信度：85%｜异常面积占比：0.00%｜异常像素：0 px｜整体一致性：高｜判定位置：全局扫描</t>
   </si>
   <si>
-    <t>bottle/test/good/001.png</t>
-  </si>
-  <si>
     <t>BOT_NG_L01</t>
   </si>
   <si>
     <t>污染</t>
   </si>
   <si>
-    <t>bottle/test/good/006.png</t>
-  </si>
-  <si>
     <t>BOT_NG_L02</t>
   </si>
   <si>
@@ -467,9 +452,6 @@
     <t>置信度：86%｜异常面积占比：0.00%｜异常像素：0 px｜整体一致性：高｜判定位置：全局扫描</t>
   </si>
   <si>
-    <t>bottle/test/good/011.png</t>
-  </si>
-  <si>
     <t>BOT_NG_L03</t>
   </si>
   <si>
@@ -479,18 +461,12 @@
     <t>置信度：65%｜异常面积占比：0.00%｜异常像素：0 px｜主异常位置：中心区域｜异常显著性：低</t>
   </si>
   <si>
-    <t>bottle/test/good/012.png</t>
-  </si>
-  <si>
     <t>BOT_NG_L04</t>
   </si>
   <si>
     <t>置信度：91%｜异常面积占比：0.00%｜异常像素：0 px｜整体一致性：高｜判定位置：全局扫描</t>
   </si>
   <si>
-    <t>bottle/test/good/002.png</t>
-  </si>
-  <si>
     <t>BOT_OK_H01</t>
   </si>
   <si>
@@ -515,30 +491,18 @@
     <t>系统检测到右侧存在可疑异常特征，瓶体与正常样本存在差异，综合判断为不合格。</t>
   </si>
   <si>
-    <t>bottle/test/contamination/019.png</t>
-  </si>
-  <si>
     <t>BOT_NG_H02</t>
   </si>
   <si>
-    <t>bottle/test/broken_small/000.png</t>
-  </si>
-  <si>
     <t>BOT_NG_H03</t>
   </si>
   <si>
     <t>系统在中心区域检测到污染/附着异常，瓶体与正常模板相比存在可分辨差异，异常区域约占图像13.78%。综合异常位置、面积与形态特征，判定为不合格。</t>
   </si>
   <si>
-    <t>bottle/test/contamination/009.png</t>
-  </si>
-  <si>
     <t>BOT_NG_H04</t>
   </si>
   <si>
-    <t>bottle/test/broken_small/014.png</t>
-  </si>
-  <si>
     <t>CAP_OK_L01</t>
   </si>
   <si>
@@ -551,9 +515,6 @@
     <t>系统检测到中心区域存在可疑异常特征，胶囊表面与正常样本存在差异，综合判断为不合格。</t>
   </si>
   <si>
-    <t>capsule/test/good/001.png</t>
-  </si>
-  <si>
     <t>CAP_OK_L02</t>
   </si>
   <si>
@@ -563,21 +524,12 @@
     <t>系统未检测到稳定且连续的异常区域，胶囊表面整体轮廓、纹理或表面状态处于可接受波动范围内，因此判定为合格。</t>
   </si>
   <si>
-    <t>capsule/test/good/006.png</t>
-  </si>
-  <si>
     <t>CAP_OK_L03</t>
   </si>
   <si>
-    <t>capsule/test/good/007.png</t>
-  </si>
-  <si>
     <t>CAP_OK_L04</t>
   </si>
   <si>
-    <t>capsule/test/good/020.png</t>
-  </si>
-  <si>
     <t>CAP_NG_L01</t>
   </si>
   <si>
@@ -593,9 +545,6 @@
     <t>系统在左侧检测到裂缝，胶囊表面与正常模板相比存在可分辨差异，异常区域约占图像2.33%。综合异常位置、面积与形态特征，判定为不合格。</t>
   </si>
   <si>
-    <t>capsule/test/crack/001.png</t>
-  </si>
-  <si>
     <t>CAP_NG_L02</t>
   </si>
   <si>
@@ -605,18 +554,12 @@
     <t>系统在中心区域检测到裂缝，胶囊表面与正常模板相比存在可分辨差异，异常区域约占图像1.80%。综合异常位置、面积与形态特征，判定为不合格。</t>
   </si>
   <si>
-    <t>capsule/test/crack/010.png</t>
-  </si>
-  <si>
     <t>CAP_NG_L03</t>
   </si>
   <si>
     <t>挤压变形</t>
   </si>
   <si>
-    <t>capsule/test/squeeze/007.png</t>
-  </si>
-  <si>
     <t>CAP_NG_L04</t>
   </si>
   <si>
@@ -632,36 +575,21 @@
     <t>系统在右侧检测到针孔，胶囊表面与正常模板相比存在可分辨差异，异常区域约占图像1.23%。综合异常位置、面积与形态特征，判定为不合格。</t>
   </si>
   <si>
-    <t>capsule/test/poke/000.png</t>
-  </si>
-  <si>
     <t>CAP_OK_H01</t>
   </si>
   <si>
-    <t>capsule/test/good/002.png</t>
-  </si>
-  <si>
     <t>CAP_OK_H02</t>
   </si>
   <si>
-    <t>capsule/test/good/005.png</t>
-  </si>
-  <si>
     <t>CAP_OK_H03</t>
   </si>
   <si>
-    <t>capsule/test/good/012.png</t>
-  </si>
-  <si>
     <t>CAP_OK_H04</t>
   </si>
   <si>
     <t>置信度：90%｜异常面积占比：0.00%｜异常像素：0 px｜整体一致性：高｜判定位置：全局扫描</t>
   </si>
   <si>
-    <t>capsule/test/good/014.png</t>
-  </si>
-  <si>
     <t>CAP_NG_H01</t>
   </si>
   <si>
@@ -671,9 +599,6 @@
     <t>系统在中心区域检测到针孔，胶囊表面与正常模板相比存在可分辨差异，异常区域约占图像0.16%。综合异常位置、面积与形态特征，判定为不合格。</t>
   </si>
   <si>
-    <t>capsule/test/poke/006.png</t>
-  </si>
-  <si>
     <t>CAP_NG_H02</t>
   </si>
   <si>
@@ -683,18 +608,12 @@
     <t>系统在右侧检测到针孔，胶囊表面与正常模板相比存在可分辨差异，异常区域约占图像0.29%。综合异常位置、面积与形态特征，判定为不合格。</t>
   </si>
   <si>
-    <t>capsule/test/poke/012.png</t>
-  </si>
-  <si>
     <t>CAP_NG_H03</t>
   </si>
   <si>
     <t>划痕</t>
   </si>
   <si>
-    <t>capsule/test/scratch/002.png</t>
-  </si>
-  <si>
     <t>CAP_NG_H04</t>
   </si>
   <si>
@@ -704,9 +623,6 @@
     <t>系统在中心区域检测到划痕，胶囊表面与正常模板相比存在可分辨差异，异常区域约占图像0.30%。综合异常位置、面积与形态特征，判定为不合格。</t>
   </si>
   <si>
-    <t>capsule/test/scratch/005.png</t>
-  </si>
-  <si>
     <t>MET_OK_L01</t>
   </si>
   <si>
@@ -722,30 +638,18 @@
     <t>系统未检测到稳定且连续的异常区域，螺母表面与边缘整体轮廓、纹理或表面状态处于可接受波动范围内，因此判定为合格。</t>
   </si>
   <si>
-    <t>metal_nut/test/good/004.png</t>
-  </si>
-  <si>
     <t>MET_OK_L02</t>
   </si>
   <si>
     <t>系统检测到中心区域存在可疑异常特征，螺母表面与边缘与正常样本存在差异，综合判断为不合格。</t>
   </si>
   <si>
-    <t>metal_nut/test/good/009.png</t>
-  </si>
-  <si>
     <t>MET_OK_L03</t>
   </si>
   <si>
-    <t>metal_nut/test/good/016.png</t>
-  </si>
-  <si>
     <t>MET_OK_L04</t>
   </si>
   <si>
-    <t>metal_nut/test/good/020.png</t>
-  </si>
-  <si>
     <t>MET_NG_L01</t>
   </si>
   <si>
@@ -761,9 +665,6 @@
     <t>系统在上部检测到弯曲变形，螺母表面与边缘与正常模板相比存在可分辨差异，异常区域约占图像4.70%。综合异常位置、面积与形态特征，判定为不合格。</t>
   </si>
   <si>
-    <t>metal_nut/test/bent/000.png</t>
-  </si>
-  <si>
     <t>MET_NG_L02</t>
   </si>
   <si>
@@ -779,15 +680,9 @@
     <t>系统在右侧检测到局部色差，螺母表面与边缘与正常模板相比存在可分辨差异，异常区域约占图像2.28%。综合异常位置、面积与形态特征，判定为不合格。</t>
   </si>
   <si>
-    <t>metal_nut/test/color/019.png</t>
-  </si>
-  <si>
     <t>MET_NG_L03</t>
   </si>
   <si>
-    <t>metal_nut/test/color/011.png</t>
-  </si>
-  <si>
     <t>MET_NG_L04</t>
   </si>
   <si>
@@ -797,9 +692,6 @@
     <t>系统在上部右侧检测到局部色差，螺母表面与边缘与正常模板相比存在可分辨差异，异常区域约占图像6.57%。综合异常位置、面积与形态特征，判定为不合格。</t>
   </si>
   <si>
-    <t>metal_nut/test/color/012.png</t>
-  </si>
-  <si>
     <t>MET_OK_H01</t>
   </si>
   <si>
@@ -809,9 +701,6 @@
     <t>系统在下部左侧检测到弯曲变形，螺母表面与边缘与正常模板相比存在可分辨差异，异常区域约占图像2.01%。综合异常位置、面积与形态特征，判定为不合格。</t>
   </si>
   <si>
-    <t>metal_nut/test/bent/021.png</t>
-  </si>
-  <si>
     <t>MET_OK_H02</t>
   </si>
   <si>
@@ -824,15 +713,9 @@
     <t>系统在下部检测到划痕，螺母表面与边缘与正常模板相比存在可分辨差异，异常区域约占图像7.37%。综合异常位置、面积与形态特征，判定为不合格。</t>
   </si>
   <si>
-    <t>metal_nut/test/scratch/022.png</t>
-  </si>
-  <si>
     <t>MET_OK_H03</t>
   </si>
   <si>
-    <t>metal_nut/test/bent/014.png</t>
-  </si>
-  <si>
     <t>MET_OK_H04</t>
   </si>
   <si>
@@ -845,9 +728,6 @@
     <t>系统在中心区域检测到朝向异常，螺母表面与边缘与正常模板相比存在可分辨差异，异常区域约占图像48.16%。综合异常位置、面积与形态特征，判定为不合格。</t>
   </si>
   <si>
-    <t>metal_nut/test/flip/022.png</t>
-  </si>
-  <si>
     <t>MET_NG_H01</t>
   </si>
   <si>
@@ -1100,9 +980,6 @@
     <t>实验一</t>
   </si>
   <si>
-    <t>practice/1_001.png</t>
-  </si>
-  <si>
     <t>OK/NG判断</t>
   </si>
   <si>
@@ -1112,27 +989,15 @@
     <t>练习题结束后建议向被试展示此反馈</t>
   </si>
   <si>
-    <t>practice/1_002.png</t>
-  </si>
-  <si>
-    <t>practice/1_003.png</t>
-  </si>
-  <si>
     <t>正确答案：OK（合格）。AI 认为该胶囊为 OK（合格），依据是图像中未见明显异常，产品外观与标准样本一致。</t>
   </si>
   <si>
-    <t>practice/1_004.png</t>
-  </si>
-  <si>
     <t>实验二</t>
   </si>
   <si>
     <t>BOT_BUY_L01</t>
   </si>
   <si>
-    <t>practice/2_001.png</t>
-  </si>
-  <si>
     <t>采购判断</t>
   </si>
   <si>
@@ -1142,25 +1007,16 @@
     <t>BOT_BUY_L08</t>
   </si>
   <si>
-    <t>practice/2_002.png</t>
-  </si>
-  <si>
     <t>标准答案：不采购。质量分=44，成本分=30.0，综合分=39.8。先检查质量是否过线，再综合考虑成本。</t>
   </si>
   <si>
     <t>CAP_BUY_L05</t>
   </si>
   <si>
-    <t>practice/2_003.png</t>
-  </si>
-  <si>
     <t>标准答案：不采购。质量分=66，成本分=45.0，综合分=59.7。先检查质量是否过线，再综合考虑成本。</t>
   </si>
   <si>
     <t>MET_BUY_L04</t>
-  </si>
-  <si>
-    <t>practice/2_004.png</t>
   </si>
   <si>
     <t>正确答案：NG（不合格）。AI 认为该瓶子为 NG（不合格），依据是图像中可见明显异常，产品外观有污染缺陷，与标准样本不一致。</t>
@@ -1287,22 +1143,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>metal_nut/test/good/005.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>metal_nut/test/good/007.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>metal_nut/test/good/008.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>metal_nut/test/good/012.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>标准答案：不采购。质量分=55，成本分=64.6，综合分=57.88。先检查质量是否过线，再综合考虑成本。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1634,6 +1474,30 @@
   </si>
   <si>
     <t>metal_nut/test/good/012.jpg</t>
+  </si>
+  <si>
+    <t>practice/1_001.jpg</t>
+  </si>
+  <si>
+    <t>practice/1_002.jpg</t>
+  </si>
+  <si>
+    <t>practice/1_003.jpg</t>
+  </si>
+  <si>
+    <t>practice/1_004.jpg</t>
+  </si>
+  <si>
+    <t>practice/2_001.jpg</t>
+  </si>
+  <si>
+    <t>practice/2_002.jpg</t>
+  </si>
+  <si>
+    <t>practice/2_003.jpg</t>
+  </si>
+  <si>
+    <t>practice/2_004.jpg</t>
   </si>
 </sst>
 </file>
@@ -2586,16 +2450,16 @@
         <v>119</v>
       </c>
       <c r="P2" t="s">
-        <v>377</v>
+        <v>329</v>
       </c>
       <c r="Q2" t="s">
-        <v>392</v>
+        <v>344</v>
       </c>
       <c r="R2" t="s">
         <v>121</v>
       </c>
       <c r="S2" t="s">
-        <v>439</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
@@ -2603,7 +2467,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C3" t="s">
         <v>110</v>
@@ -2633,28 +2497,28 @@
         <v>1</v>
       </c>
       <c r="L3" t="s">
+        <v>123</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3" t="s">
         <v>124</v>
       </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>125</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>126</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>127</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>128</v>
       </c>
       <c r="R3" t="s">
         <v>121</v>
       </c>
       <c r="S3" t="s">
-        <v>440</v>
+        <v>388</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
@@ -2662,7 +2526,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C4" t="s">
         <v>110</v>
@@ -2692,28 +2556,28 @@
         <v>1</v>
       </c>
       <c r="L4" t="s">
+        <v>123</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4" t="s">
         <v>124</v>
       </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>125</v>
       </c>
-      <c r="O4" t="s">
-        <v>126</v>
-      </c>
       <c r="P4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="Q4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R4" t="s">
         <v>121</v>
       </c>
       <c r="S4" t="s">
-        <v>441</v>
+        <v>389</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
@@ -2721,7 +2585,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C5" t="s">
         <v>110</v>
@@ -2751,28 +2615,28 @@
         <v>1</v>
       </c>
       <c r="L5" t="s">
+        <v>123</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5" t="s">
         <v>124</v>
       </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-      <c r="N5" t="s">
+      <c r="O5" t="s">
         <v>125</v>
       </c>
-      <c r="O5" t="s">
-        <v>126</v>
-      </c>
       <c r="P5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="Q5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R5" t="s">
         <v>121</v>
       </c>
       <c r="S5" t="s">
-        <v>442</v>
+        <v>390</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
@@ -2780,7 +2644,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C6" t="s">
         <v>110</v>
@@ -2789,7 +2653,7 @@
         <v>111</v>
       </c>
       <c r="E6" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F6" t="s">
         <v>113</v>
@@ -2810,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -2819,19 +2683,19 @@
         <v>118</v>
       </c>
       <c r="O6" t="s">
-        <v>382</v>
+        <v>334</v>
       </c>
       <c r="P6" t="s">
-        <v>378</v>
+        <v>330</v>
       </c>
       <c r="Q6" t="s">
-        <v>380</v>
+        <v>332</v>
       </c>
       <c r="R6" t="s">
-        <v>438</v>
+        <v>386</v>
       </c>
       <c r="S6" t="s">
-        <v>443</v>
+        <v>391</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
@@ -2839,7 +2703,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C7" t="s">
         <v>110</v>
@@ -2848,7 +2712,7 @@
         <v>111</v>
       </c>
       <c r="E7" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F7" t="s">
         <v>113</v>
@@ -2869,7 +2733,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M7">
         <v>1</v>
@@ -2878,19 +2742,19 @@
         <v>118</v>
       </c>
       <c r="O7" t="s">
-        <v>383</v>
+        <v>335</v>
       </c>
       <c r="P7" t="s">
-        <v>385</v>
+        <v>337</v>
       </c>
       <c r="Q7" t="s">
-        <v>381</v>
+        <v>333</v>
       </c>
       <c r="R7" t="s">
-        <v>444</v>
+        <v>392</v>
       </c>
       <c r="S7" t="s">
-        <v>445</v>
+        <v>393</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
@@ -2898,7 +2762,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C8" t="s">
         <v>110</v>
@@ -2907,7 +2771,7 @@
         <v>111</v>
       </c>
       <c r="E8" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F8" t="s">
         <v>113</v>
@@ -2928,7 +2792,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M8">
         <v>1</v>
@@ -2940,16 +2804,16 @@
         <v>119</v>
       </c>
       <c r="P8" t="s">
-        <v>386</v>
+        <v>338</v>
       </c>
       <c r="Q8" t="s">
-        <v>379</v>
+        <v>331</v>
       </c>
       <c r="R8" t="s">
-        <v>446</v>
+        <v>394</v>
       </c>
       <c r="S8" t="s">
-        <v>447</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
@@ -2957,7 +2821,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C9" t="s">
         <v>110</v>
@@ -2966,7 +2830,7 @@
         <v>111</v>
       </c>
       <c r="E9" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F9" t="s">
         <v>113</v>
@@ -2993,22 +2857,22 @@
         <v>0</v>
       </c>
       <c r="N9" t="s">
+        <v>124</v>
+      </c>
+      <c r="O9" t="s">
         <v>125</v>
       </c>
-      <c r="O9" t="s">
-        <v>126</v>
-      </c>
       <c r="P9" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="Q9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R9" t="s">
-        <v>448</v>
+        <v>396</v>
       </c>
       <c r="S9" t="s">
-        <v>449</v>
+        <v>397</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -3016,7 +2880,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C10" t="s">
         <v>110</v>
@@ -3028,10 +2892,10 @@
         <v>112</v>
       </c>
       <c r="F10" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G10" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H10" t="s">
         <v>115</v>
@@ -3058,16 +2922,16 @@
         <v>119</v>
       </c>
       <c r="P10" t="s">
-        <v>376</v>
+        <v>328</v>
       </c>
       <c r="Q10" t="s">
-        <v>393</v>
+        <v>345</v>
       </c>
       <c r="R10" t="s">
         <v>121</v>
       </c>
       <c r="S10" t="s">
-        <v>450</v>
+        <v>398</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
@@ -3075,7 +2939,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C11" t="s">
         <v>110</v>
@@ -3087,10 +2951,10 @@
         <v>112</v>
       </c>
       <c r="F11" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G11" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H11" t="s">
         <v>115</v>
@@ -3105,28 +2969,28 @@
         <v>1</v>
       </c>
       <c r="L11" t="s">
+        <v>123</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11" t="s">
         <v>124</v>
       </c>
-      <c r="M11">
-        <v>1</v>
-      </c>
-      <c r="N11" t="s">
+      <c r="O11" t="s">
         <v>125</v>
       </c>
-      <c r="O11" t="s">
-        <v>126</v>
-      </c>
       <c r="P11" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="Q11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R11" t="s">
         <v>121</v>
       </c>
       <c r="S11" t="s">
-        <v>451</v>
+        <v>399</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
@@ -3134,7 +2998,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C12" t="s">
         <v>110</v>
@@ -3146,10 +3010,10 @@
         <v>112</v>
       </c>
       <c r="F12" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G12" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H12" t="s">
         <v>115</v>
@@ -3164,28 +3028,28 @@
         <v>1</v>
       </c>
       <c r="L12" t="s">
+        <v>123</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12" t="s">
         <v>124</v>
       </c>
-      <c r="M12">
-        <v>1</v>
-      </c>
-      <c r="N12" t="s">
+      <c r="O12" t="s">
         <v>125</v>
       </c>
-      <c r="O12" t="s">
-        <v>126</v>
-      </c>
       <c r="P12" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="Q12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R12" t="s">
         <v>121</v>
       </c>
       <c r="S12" t="s">
-        <v>452</v>
+        <v>400</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
@@ -3193,7 +3057,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C13" t="s">
         <v>110</v>
@@ -3205,10 +3069,10 @@
         <v>112</v>
       </c>
       <c r="F13" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G13" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H13" t="s">
         <v>115</v>
@@ -3223,28 +3087,28 @@
         <v>1</v>
       </c>
       <c r="L13" t="s">
+        <v>123</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13" t="s">
         <v>124</v>
       </c>
-      <c r="M13">
-        <v>1</v>
-      </c>
-      <c r="N13" t="s">
+      <c r="O13" t="s">
         <v>125</v>
       </c>
-      <c r="O13" t="s">
-        <v>126</v>
-      </c>
       <c r="P13" t="s">
-        <v>375</v>
+        <v>327</v>
       </c>
       <c r="Q13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R13" t="s">
         <v>121</v>
       </c>
       <c r="S13" t="s">
-        <v>453</v>
+        <v>401</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
@@ -3252,7 +3116,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C14" t="s">
         <v>110</v>
@@ -3261,13 +3125,13 @@
         <v>111</v>
       </c>
       <c r="E14" t="s">
+        <v>138</v>
+      </c>
+      <c r="F14" t="s">
+        <v>143</v>
+      </c>
+      <c r="G14" t="s">
         <v>144</v>
-      </c>
-      <c r="F14" t="s">
-        <v>151</v>
-      </c>
-      <c r="G14" t="s">
-        <v>152</v>
       </c>
       <c r="H14" t="s">
         <v>116</v>
@@ -3282,7 +3146,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M14">
         <v>1</v>
@@ -3291,19 +3155,19 @@
         <v>118</v>
       </c>
       <c r="O14" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="P14" t="s">
-        <v>389</v>
+        <v>341</v>
       </c>
       <c r="Q14" t="s">
-        <v>388</v>
+        <v>340</v>
       </c>
       <c r="R14" t="s">
-        <v>454</v>
+        <v>402</v>
       </c>
       <c r="S14" t="s">
-        <v>455</v>
+        <v>403</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
@@ -3311,7 +3175,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="C15" t="s">
         <v>110</v>
@@ -3320,13 +3184,13 @@
         <v>111</v>
       </c>
       <c r="E15" t="s">
+        <v>138</v>
+      </c>
+      <c r="F15" t="s">
+        <v>143</v>
+      </c>
+      <c r="G15" t="s">
         <v>144</v>
-      </c>
-      <c r="F15" t="s">
-        <v>151</v>
-      </c>
-      <c r="G15" t="s">
-        <v>152</v>
       </c>
       <c r="H15" t="s">
         <v>116</v>
@@ -3341,7 +3205,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M15">
         <v>1</v>
@@ -3350,19 +3214,19 @@
         <v>118</v>
       </c>
       <c r="O15" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="P15" t="s">
-        <v>390</v>
+        <v>342</v>
       </c>
       <c r="Q15" t="s">
-        <v>391</v>
+        <v>343</v>
       </c>
       <c r="R15" t="s">
-        <v>456</v>
+        <v>404</v>
       </c>
       <c r="S15" t="s">
-        <v>457</v>
+        <v>405</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -3370,7 +3234,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="C16" t="s">
         <v>110</v>
@@ -3379,13 +3243,13 @@
         <v>111</v>
       </c>
       <c r="E16" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F16" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G16" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H16" t="s">
         <v>116</v>
@@ -3400,7 +3264,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M16">
         <v>1</v>
@@ -3412,16 +3276,16 @@
         <v>119</v>
       </c>
       <c r="P16" t="s">
-        <v>387</v>
+        <v>339</v>
       </c>
       <c r="Q16" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="R16" t="s">
-        <v>458</v>
+        <v>406</v>
       </c>
       <c r="S16" t="s">
-        <v>459</v>
+        <v>407</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
@@ -3429,7 +3293,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C17" t="s">
         <v>110</v>
@@ -3438,13 +3302,13 @@
         <v>111</v>
       </c>
       <c r="E17" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F17" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G17" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H17" t="s">
         <v>116</v>
@@ -3465,22 +3329,22 @@
         <v>0</v>
       </c>
       <c r="N17" t="s">
+        <v>124</v>
+      </c>
+      <c r="O17" t="s">
         <v>125</v>
       </c>
-      <c r="O17" t="s">
-        <v>126</v>
-      </c>
       <c r="P17" t="s">
-        <v>384</v>
+        <v>336</v>
       </c>
       <c r="Q17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R17" t="s">
-        <v>460</v>
+        <v>408</v>
       </c>
       <c r="S17" t="s">
-        <v>461</v>
+        <v>409</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
@@ -3488,13 +3352,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C18" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D18" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E18" t="s">
         <v>112</v>
@@ -3527,19 +3391,19 @@
         <v>118</v>
       </c>
       <c r="O18" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="P18" t="s">
-        <v>395</v>
+        <v>347</v>
       </c>
       <c r="Q18" t="s">
-        <v>392</v>
+        <v>344</v>
       </c>
       <c r="R18" t="s">
         <v>121</v>
       </c>
       <c r="S18" t="s">
-        <v>462</v>
+        <v>410</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
@@ -3547,13 +3411,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="C19" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D19" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E19" t="s">
         <v>112</v>
@@ -3577,28 +3441,28 @@
         <v>1</v>
       </c>
       <c r="L19" t="s">
+        <v>123</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19" t="s">
         <v>124</v>
       </c>
-      <c r="M19">
-        <v>1</v>
-      </c>
-      <c r="N19" t="s">
-        <v>125</v>
-      </c>
       <c r="O19" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="P19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q19" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="R19" t="s">
         <v>121</v>
       </c>
       <c r="S19" t="s">
-        <v>463</v>
+        <v>411</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
@@ -3606,13 +3470,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="C20" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D20" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E20" t="s">
         <v>112</v>
@@ -3636,28 +3500,28 @@
         <v>1</v>
       </c>
       <c r="L20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20" t="s">
         <v>124</v>
       </c>
-      <c r="M20">
-        <v>1</v>
-      </c>
-      <c r="N20" t="s">
-        <v>125</v>
-      </c>
       <c r="O20" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="P20" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="Q20" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="R20" t="s">
         <v>121</v>
       </c>
       <c r="S20" t="s">
-        <v>464</v>
+        <v>412</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
@@ -3665,13 +3529,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="C21" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D21" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E21" t="s">
         <v>112</v>
@@ -3695,28 +3559,28 @@
         <v>1</v>
       </c>
       <c r="L21" t="s">
+        <v>123</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21" t="s">
         <v>124</v>
       </c>
-      <c r="M21">
-        <v>1</v>
-      </c>
-      <c r="N21" t="s">
-        <v>125</v>
-      </c>
       <c r="O21" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="P21" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="Q21" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="R21" t="s">
         <v>121</v>
       </c>
       <c r="S21" t="s">
-        <v>465</v>
+        <v>413</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
@@ -3724,16 +3588,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="C22" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D22" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E22" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="F22" t="s">
         <v>113</v>
@@ -3754,7 +3618,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M22">
         <v>1</v>
@@ -3763,19 +3627,19 @@
         <v>118</v>
       </c>
       <c r="O22" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="P22" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="Q22" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="R22" t="s">
-        <v>466</v>
+        <v>414</v>
       </c>
       <c r="S22" t="s">
-        <v>467</v>
+        <v>415</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
@@ -3783,16 +3647,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="C23" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D23" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E23" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="F23" t="s">
         <v>113</v>
@@ -3813,7 +3677,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M23">
         <v>1</v>
@@ -3822,19 +3686,19 @@
         <v>118</v>
       </c>
       <c r="O23" t="s">
+        <v>157</v>
+      </c>
+      <c r="P23" t="s">
         <v>169</v>
       </c>
-      <c r="P23" t="s">
-        <v>186</v>
-      </c>
       <c r="Q23" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="R23" t="s">
-        <v>468</v>
+        <v>416</v>
       </c>
       <c r="S23" t="s">
-        <v>469</v>
+        <v>417</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
@@ -3842,16 +3706,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="C24" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D24" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E24" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="F24" t="s">
         <v>113</v>
@@ -3878,22 +3742,22 @@
         <v>0</v>
       </c>
       <c r="N24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O24" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="P24" t="s">
-        <v>398</v>
+        <v>350</v>
       </c>
       <c r="Q24" t="s">
-        <v>400</v>
+        <v>352</v>
       </c>
       <c r="R24" t="s">
-        <v>470</v>
+        <v>418</v>
       </c>
       <c r="S24" t="s">
-        <v>471</v>
+        <v>419</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
@@ -3901,16 +3765,16 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="C25" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D25" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E25" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="F25" t="s">
         <v>113</v>
@@ -3931,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M25">
         <v>1</v>
@@ -3940,19 +3804,19 @@
         <v>118</v>
       </c>
       <c r="O25" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="P25" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="Q25" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="R25" t="s">
-        <v>472</v>
+        <v>420</v>
       </c>
       <c r="S25" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
@@ -3960,22 +3824,22 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="C26" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D26" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E26" t="s">
         <v>112</v>
       </c>
       <c r="F26" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G26" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H26" t="s">
         <v>115</v>
@@ -3999,19 +3863,19 @@
         <v>118</v>
       </c>
       <c r="O26" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="P26" t="s">
-        <v>396</v>
+        <v>348</v>
       </c>
       <c r="Q26" t="s">
-        <v>397</v>
+        <v>349</v>
       </c>
       <c r="R26" t="s">
         <v>121</v>
       </c>
       <c r="S26" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
@@ -4019,22 +3883,22 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="C27" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D27" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E27" t="s">
         <v>112</v>
       </c>
       <c r="F27" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G27" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H27" t="s">
         <v>115</v>
@@ -4049,28 +3913,28 @@
         <v>1</v>
       </c>
       <c r="L27" t="s">
+        <v>123</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
+      </c>
+      <c r="N27" t="s">
         <v>124</v>
       </c>
-      <c r="M27">
-        <v>1</v>
-      </c>
-      <c r="N27" t="s">
-        <v>125</v>
-      </c>
       <c r="O27" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="P27" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="Q27" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="R27" t="s">
         <v>121</v>
       </c>
       <c r="S27" t="s">
-        <v>475</v>
+        <v>423</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
@@ -4078,22 +3942,22 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="C28" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D28" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E28" t="s">
         <v>112</v>
       </c>
       <c r="F28" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G28" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H28" t="s">
         <v>115</v>
@@ -4108,28 +3972,28 @@
         <v>1</v>
       </c>
       <c r="L28" t="s">
+        <v>123</v>
+      </c>
+      <c r="M28">
+        <v>1</v>
+      </c>
+      <c r="N28" t="s">
         <v>124</v>
       </c>
-      <c r="M28">
-        <v>1</v>
-      </c>
-      <c r="N28" t="s">
-        <v>125</v>
-      </c>
       <c r="O28" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="P28" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="Q28" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="R28" t="s">
         <v>121</v>
       </c>
       <c r="S28" t="s">
-        <v>476</v>
+        <v>424</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
@@ -4137,22 +4001,22 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="C29" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D29" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E29" t="s">
         <v>112</v>
       </c>
       <c r="F29" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G29" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H29" t="s">
         <v>115</v>
@@ -4167,28 +4031,28 @@
         <v>1</v>
       </c>
       <c r="L29" t="s">
+        <v>123</v>
+      </c>
+      <c r="M29">
+        <v>1</v>
+      </c>
+      <c r="N29" t="s">
         <v>124</v>
       </c>
-      <c r="M29">
-        <v>1</v>
-      </c>
-      <c r="N29" t="s">
-        <v>125</v>
-      </c>
       <c r="O29" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="P29" t="s">
-        <v>205</v>
+        <v>182</v>
       </c>
       <c r="Q29" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="R29" t="s">
         <v>121</v>
       </c>
       <c r="S29" t="s">
-        <v>477</v>
+        <v>425</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
@@ -4196,22 +4060,22 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="C30" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D30" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E30" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="F30" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G30" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H30" t="s">
         <v>116</v>
@@ -4226,7 +4090,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M30">
         <v>1</v>
@@ -4235,19 +4099,19 @@
         <v>118</v>
       </c>
       <c r="O30" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="P30" t="s">
-        <v>208</v>
+        <v>184</v>
       </c>
       <c r="Q30" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="R30" t="s">
-        <v>478</v>
+        <v>426</v>
       </c>
       <c r="S30" t="s">
-        <v>479</v>
+        <v>427</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
@@ -4255,22 +4119,22 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>211</v>
+        <v>186</v>
       </c>
       <c r="C31" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D31" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E31" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="F31" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G31" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H31" t="s">
         <v>116</v>
@@ -4285,7 +4149,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M31">
         <v>1</v>
@@ -4294,19 +4158,19 @@
         <v>118</v>
       </c>
       <c r="O31" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="P31" t="s">
-        <v>212</v>
+        <v>187</v>
       </c>
       <c r="Q31" t="s">
-        <v>213</v>
+        <v>188</v>
       </c>
       <c r="R31" t="s">
-        <v>480</v>
+        <v>428</v>
       </c>
       <c r="S31" t="s">
-        <v>481</v>
+        <v>429</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
@@ -4314,22 +4178,22 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
       <c r="C32" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D32" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E32" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="F32" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G32" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H32" t="s">
         <v>116</v>
@@ -4350,22 +4214,22 @@
         <v>0</v>
       </c>
       <c r="N32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O32" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="P32" t="s">
-        <v>399</v>
+        <v>351</v>
       </c>
       <c r="Q32" t="s">
-        <v>400</v>
+        <v>352</v>
       </c>
       <c r="R32" t="s">
-        <v>482</v>
+        <v>430</v>
       </c>
       <c r="S32" t="s">
-        <v>483</v>
+        <v>431</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
@@ -4373,22 +4237,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="C33" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D33" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E33" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="F33" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G33" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H33" t="s">
         <v>116</v>
@@ -4403,7 +4267,7 @@
         <v>0</v>
       </c>
       <c r="L33" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M33">
         <v>1</v>
@@ -4412,19 +4276,19 @@
         <v>118</v>
       </c>
       <c r="O33" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="P33" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="Q33" t="s">
-        <v>220</v>
+        <v>193</v>
       </c>
       <c r="R33" t="s">
-        <v>484</v>
+        <v>432</v>
       </c>
       <c r="S33" t="s">
-        <v>485</v>
+        <v>433</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
@@ -4432,13 +4296,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>222</v>
+        <v>194</v>
       </c>
       <c r="C34" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D34" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E34" t="s">
         <v>112</v>
@@ -4462,28 +4326,28 @@
         <v>1</v>
       </c>
       <c r="L34" t="s">
+        <v>123</v>
+      </c>
+      <c r="M34">
+        <v>1</v>
+      </c>
+      <c r="N34" t="s">
         <v>124</v>
       </c>
-      <c r="M34">
-        <v>1</v>
-      </c>
-      <c r="N34" t="s">
-        <v>125</v>
-      </c>
       <c r="O34" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
       <c r="P34" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q34" t="s">
-        <v>226</v>
+        <v>198</v>
       </c>
       <c r="R34" t="s">
         <v>121</v>
       </c>
       <c r="S34" t="s">
-        <v>486</v>
+        <v>434</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
@@ -4491,13 +4355,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>228</v>
+        <v>199</v>
       </c>
       <c r="C35" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D35" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E35" t="s">
         <v>112</v>
@@ -4530,10 +4394,10 @@
         <v>118</v>
       </c>
       <c r="O35" t="s">
-        <v>229</v>
+        <v>200</v>
       </c>
       <c r="P35" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="Q35" t="s">
         <v>120</v>
@@ -4542,7 +4406,7 @@
         <v>121</v>
       </c>
       <c r="S35" t="s">
-        <v>487</v>
+        <v>435</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
@@ -4550,13 +4414,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
       <c r="C36" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D36" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E36" t="s">
         <v>112</v>
@@ -4580,28 +4444,28 @@
         <v>1</v>
       </c>
       <c r="L36" t="s">
+        <v>123</v>
+      </c>
+      <c r="M36">
+        <v>1</v>
+      </c>
+      <c r="N36" t="s">
         <v>124</v>
       </c>
-      <c r="M36">
-        <v>1</v>
-      </c>
-      <c r="N36" t="s">
-        <v>125</v>
-      </c>
       <c r="O36" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
       <c r="P36" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="Q36" t="s">
-        <v>226</v>
+        <v>198</v>
       </c>
       <c r="R36" t="s">
         <v>121</v>
       </c>
       <c r="S36" t="s">
-        <v>488</v>
+        <v>436</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
@@ -4609,13 +4473,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>233</v>
+        <v>202</v>
       </c>
       <c r="C37" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D37" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E37" t="s">
         <v>112</v>
@@ -4639,28 +4503,28 @@
         <v>1</v>
       </c>
       <c r="L37" t="s">
+        <v>123</v>
+      </c>
+      <c r="M37">
+        <v>1</v>
+      </c>
+      <c r="N37" t="s">
         <v>124</v>
       </c>
-      <c r="M37">
-        <v>1</v>
-      </c>
-      <c r="N37" t="s">
-        <v>125</v>
-      </c>
       <c r="O37" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
       <c r="P37" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="Q37" t="s">
-        <v>226</v>
+        <v>198</v>
       </c>
       <c r="R37" t="s">
         <v>121</v>
       </c>
       <c r="S37" t="s">
-        <v>489</v>
+        <v>437</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
@@ -4668,16 +4532,16 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>235</v>
+        <v>203</v>
       </c>
       <c r="C38" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D38" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E38" t="s">
-        <v>236</v>
+        <v>204</v>
       </c>
       <c r="F38" t="s">
         <v>113</v>
@@ -4698,7 +4562,7 @@
         <v>0</v>
       </c>
       <c r="L38" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M38">
         <v>1</v>
@@ -4707,19 +4571,19 @@
         <v>118</v>
       </c>
       <c r="O38" t="s">
-        <v>237</v>
+        <v>205</v>
       </c>
       <c r="P38" t="s">
-        <v>238</v>
+        <v>206</v>
       </c>
       <c r="Q38" t="s">
-        <v>239</v>
+        <v>207</v>
       </c>
       <c r="R38" t="s">
-        <v>490</v>
+        <v>438</v>
       </c>
       <c r="S38" t="s">
-        <v>491</v>
+        <v>439</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
@@ -4727,16 +4591,16 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>241</v>
+        <v>208</v>
       </c>
       <c r="C39" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D39" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E39" t="s">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="F39" t="s">
         <v>113</v>
@@ -4757,7 +4621,7 @@
         <v>0</v>
       </c>
       <c r="L39" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M39">
         <v>1</v>
@@ -4766,19 +4630,19 @@
         <v>118</v>
       </c>
       <c r="O39" t="s">
-        <v>243</v>
+        <v>210</v>
       </c>
       <c r="P39" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="Q39" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="R39" t="s">
-        <v>492</v>
+        <v>440</v>
       </c>
       <c r="S39" t="s">
-        <v>493</v>
+        <v>441</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
@@ -4786,16 +4650,16 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>247</v>
+        <v>213</v>
       </c>
       <c r="C40" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D40" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E40" t="s">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="F40" t="s">
         <v>113</v>
@@ -4822,22 +4686,22 @@
         <v>0</v>
       </c>
       <c r="N40" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O40" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
       <c r="P40" t="s">
-        <v>401</v>
+        <v>353</v>
       </c>
       <c r="Q40" t="s">
-        <v>400</v>
+        <v>352</v>
       </c>
       <c r="R40" t="s">
-        <v>494</v>
+        <v>442</v>
       </c>
       <c r="S40" t="s">
-        <v>495</v>
+        <v>443</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
@@ -4845,16 +4709,16 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>249</v>
+        <v>214</v>
       </c>
       <c r="C41" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D41" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E41" t="s">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="F41" t="s">
         <v>113</v>
@@ -4875,7 +4739,7 @@
         <v>0</v>
       </c>
       <c r="L41" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M41">
         <v>1</v>
@@ -4884,19 +4748,19 @@
         <v>118</v>
       </c>
       <c r="O41" t="s">
-        <v>250</v>
+        <v>215</v>
       </c>
       <c r="P41" t="s">
-        <v>402</v>
+        <v>354</v>
       </c>
       <c r="Q41" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="R41" t="s">
-        <v>496</v>
+        <v>444</v>
       </c>
       <c r="S41" t="s">
-        <v>497</v>
+        <v>445</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
@@ -4904,22 +4768,22 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>253</v>
+        <v>217</v>
       </c>
       <c r="C42" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D42" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E42" t="s">
-        <v>394</v>
+        <v>346</v>
       </c>
       <c r="F42" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G42" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H42" t="s">
         <v>115</v>
@@ -4934,28 +4798,28 @@
         <v>1</v>
       </c>
       <c r="L42" t="s">
+        <v>123</v>
+      </c>
+      <c r="M42">
+        <v>1</v>
+      </c>
+      <c r="N42" t="s">
         <v>124</v>
       </c>
-      <c r="M42">
-        <v>1</v>
-      </c>
-      <c r="N42" t="s">
-        <v>125</v>
-      </c>
       <c r="O42" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
       <c r="P42" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="Q42" t="s">
-        <v>226</v>
+        <v>198</v>
       </c>
       <c r="R42" t="s">
         <v>121</v>
       </c>
       <c r="S42" t="s">
-        <v>498</v>
+        <v>446</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
@@ -4963,22 +4827,22 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>257</v>
+        <v>220</v>
       </c>
       <c r="C43" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D43" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E43" t="s">
-        <v>394</v>
+        <v>346</v>
       </c>
       <c r="F43" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G43" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H43" t="s">
         <v>115</v>
@@ -4993,28 +4857,28 @@
         <v>1</v>
       </c>
       <c r="L43" t="s">
+        <v>123</v>
+      </c>
+      <c r="M43">
+        <v>1</v>
+      </c>
+      <c r="N43" t="s">
         <v>124</v>
       </c>
-      <c r="M43">
-        <v>1</v>
-      </c>
-      <c r="N43" t="s">
-        <v>125</v>
-      </c>
       <c r="O43" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
       <c r="P43" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="Q43" t="s">
-        <v>226</v>
+        <v>198</v>
       </c>
       <c r="R43" t="s">
         <v>121</v>
       </c>
       <c r="S43" t="s">
-        <v>499</v>
+        <v>447</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
@@ -5022,22 +4886,22 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>262</v>
+        <v>224</v>
       </c>
       <c r="C44" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D44" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E44" t="s">
-        <v>236</v>
+        <v>204</v>
       </c>
       <c r="F44" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G44" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H44" t="s">
         <v>116</v>
@@ -5052,7 +4916,7 @@
         <v>0</v>
       </c>
       <c r="L44" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M44">
         <v>1</v>
@@ -5061,19 +4925,19 @@
         <v>118</v>
       </c>
       <c r="O44" t="s">
-        <v>254</v>
+        <v>218</v>
       </c>
       <c r="P44" t="s">
-        <v>403</v>
+        <v>355</v>
       </c>
       <c r="Q44" t="s">
-        <v>255</v>
+        <v>219</v>
       </c>
       <c r="R44" t="s">
-        <v>500</v>
+        <v>448</v>
       </c>
       <c r="S44" t="s">
-        <v>501</v>
+        <v>449</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
@@ -5081,22 +4945,22 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>264</v>
+        <v>225</v>
       </c>
       <c r="C45" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D45" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E45" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="F45" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G45" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H45" t="s">
         <v>116</v>
@@ -5111,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="L45" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M45">
         <v>1</v>
@@ -5120,19 +4984,19 @@
         <v>118</v>
       </c>
       <c r="O45" t="s">
-        <v>229</v>
+        <v>200</v>
       </c>
       <c r="P45" t="s">
-        <v>266</v>
+        <v>227</v>
       </c>
       <c r="Q45" t="s">
-        <v>267</v>
+        <v>228</v>
       </c>
       <c r="R45" t="s">
-        <v>502</v>
+        <v>450</v>
       </c>
       <c r="S45" t="s">
-        <v>503</v>
+        <v>451</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
@@ -5140,22 +5004,22 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>269</v>
+        <v>229</v>
       </c>
       <c r="C46" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D46" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E46" t="s">
-        <v>236</v>
+        <v>204</v>
       </c>
       <c r="F46" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G46" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H46" t="s">
         <v>116</v>
@@ -5170,28 +5034,28 @@
         <v>1</v>
       </c>
       <c r="L46" t="s">
+        <v>123</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46" t="s">
         <v>124</v>
       </c>
-      <c r="M46">
-        <v>0</v>
-      </c>
-      <c r="N46" t="s">
-        <v>125</v>
-      </c>
       <c r="O46" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
       <c r="P46" t="s">
-        <v>404</v>
+        <v>356</v>
       </c>
       <c r="Q46" t="s">
-        <v>400</v>
+        <v>352</v>
       </c>
       <c r="R46" t="s">
-        <v>504</v>
+        <v>452</v>
       </c>
       <c r="S46" t="s">
-        <v>505</v>
+        <v>453</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
@@ -5199,22 +5063,22 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>270</v>
+        <v>230</v>
       </c>
       <c r="C47" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D47" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E47" t="s">
-        <v>265</v>
+        <v>226</v>
       </c>
       <c r="F47" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G47" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H47" t="s">
         <v>116</v>
@@ -5229,7 +5093,7 @@
         <v>0</v>
       </c>
       <c r="L47" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M47">
         <v>1</v>
@@ -5238,19 +5102,19 @@
         <v>118</v>
       </c>
       <c r="O47" t="s">
-        <v>258</v>
+        <v>221</v>
       </c>
       <c r="P47" t="s">
-        <v>259</v>
+        <v>222</v>
       </c>
       <c r="Q47" t="s">
-        <v>260</v>
+        <v>223</v>
       </c>
       <c r="R47" t="s">
-        <v>506</v>
+        <v>454</v>
       </c>
       <c r="S47" t="s">
-        <v>507</v>
+        <v>455</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
@@ -5258,22 +5122,22 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>271</v>
+        <v>231</v>
       </c>
       <c r="C48" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D48" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E48" t="s">
-        <v>394</v>
+        <v>346</v>
       </c>
       <c r="F48" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G48" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H48" t="s">
         <v>115</v>
@@ -5297,19 +5161,19 @@
         <v>118</v>
       </c>
       <c r="O48" t="s">
-        <v>258</v>
+        <v>221</v>
       </c>
       <c r="P48" t="s">
-        <v>259</v>
+        <v>222</v>
       </c>
       <c r="Q48" t="s">
-        <v>260</v>
+        <v>223</v>
       </c>
       <c r="R48" t="s">
         <v>121</v>
       </c>
       <c r="S48" t="s">
-        <v>508</v>
+        <v>456</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
@@ -5317,22 +5181,22 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>272</v>
+        <v>232</v>
       </c>
       <c r="C49" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D49" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E49" t="s">
-        <v>394</v>
+        <v>346</v>
       </c>
       <c r="F49" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G49" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H49" t="s">
         <v>115</v>
@@ -5347,28 +5211,28 @@
         <v>1</v>
       </c>
       <c r="L49" t="s">
+        <v>123</v>
+      </c>
+      <c r="M49">
+        <v>1</v>
+      </c>
+      <c r="N49" t="s">
         <v>124</v>
       </c>
-      <c r="M49">
-        <v>1</v>
-      </c>
-      <c r="N49" t="s">
-        <v>125</v>
-      </c>
       <c r="O49" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
       <c r="P49" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="Q49" t="s">
-        <v>226</v>
+        <v>198</v>
       </c>
       <c r="R49" t="s">
         <v>121</v>
       </c>
       <c r="S49" t="s">
-        <v>509</v>
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -5424,7 +5288,7 @@
         <v>47</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>410</v>
+        <v>358</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>99</v>
@@ -5451,16 +5315,16 @@
         <v>74</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>273</v>
+        <v>233</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>274</v>
+        <v>234</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>275</v>
+        <v>235</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>276</v>
+        <v>236</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>77</v>
@@ -5469,16 +5333,16 @@
         <v>80</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>277</v>
+        <v>237</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>84</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>278</v>
+        <v>238</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>279</v>
+        <v>239</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>88</v>
@@ -5487,7 +5351,7 @@
         <v>95</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>106</v>
@@ -5522,7 +5386,7 @@
         <v>114</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>122</v>
+        <v>387</v>
       </c>
       <c r="I2" s="1">
         <v>92</v>
@@ -5561,31 +5425,31 @@
         <v>采购</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="U2" s="1">
         <v>1</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="X2" s="1">
         <v>1</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>284</v>
+        <v>244</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>285</v>
+        <v>245</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
@@ -5593,7 +5457,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>110</v>
@@ -5611,7 +5475,7 @@
         <v>114</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>129</v>
+        <v>388</v>
       </c>
       <c r="I3" s="1">
         <v>85</v>
@@ -5650,31 +5514,31 @@
         <v>采购</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="U3" s="1">
         <v>1</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="X3" s="1">
         <v>1</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>287</v>
+        <v>247</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>288</v>
+        <v>248</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
@@ -5682,7 +5546,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>110</v>
@@ -5700,7 +5564,7 @@
         <v>114</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>132</v>
+        <v>389</v>
       </c>
       <c r="I4" s="1">
         <v>78</v>
@@ -5739,31 +5603,31 @@
         <v>采购</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="U4" s="1">
         <v>1</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="X4" s="1">
         <v>1</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>291</v>
+        <v>251</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>292</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
@@ -5771,7 +5635,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>110</v>
@@ -5789,7 +5653,7 @@
         <v>114</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>135</v>
+        <v>390</v>
       </c>
       <c r="I5" s="1">
         <v>72</v>
@@ -5828,31 +5692,31 @@
         <v>不采购</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="U5" s="1">
         <v>0</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="X5" s="1">
         <v>1</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>294</v>
+        <v>254</v>
       </c>
       <c r="AA5" s="1" t="s">
-        <v>295</v>
+        <v>255</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
@@ -5860,7 +5724,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>110</v>
@@ -5869,7 +5733,7 @@
         <v>111</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>113</v>
@@ -5878,7 +5742,7 @@
         <v>114</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>138</v>
+        <v>398</v>
       </c>
       <c r="I6" s="1">
         <v>66</v>
@@ -5917,31 +5781,31 @@
         <v>不采购</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="U6" s="1">
         <v>0</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="X6" s="1">
         <v>1</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>411</v>
+        <v>359</v>
       </c>
       <c r="AA6" s="1" t="s">
-        <v>297</v>
+        <v>257</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
@@ -5949,7 +5813,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>110</v>
@@ -5958,7 +5822,7 @@
         <v>111</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>113</v>
@@ -5967,7 +5831,7 @@
         <v>114</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>142</v>
+        <v>399</v>
       </c>
       <c r="I7" s="1">
         <v>78</v>
@@ -6006,31 +5870,31 @@
         <v>采购</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="U7" s="1">
         <v>1</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="X7" s="1">
         <v>1</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>413</v>
+        <v>361</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>291</v>
+        <v>251</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>292</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
@@ -6038,7 +5902,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>110</v>
@@ -6047,7 +5911,7 @@
         <v>111</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>113</v>
@@ -6056,7 +5920,7 @@
         <v>114</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>146</v>
+        <v>400</v>
       </c>
       <c r="I8" s="1">
         <v>89</v>
@@ -6095,31 +5959,31 @@
         <v>采购</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="U8" s="1">
         <v>1</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>431</v>
+        <v>379</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="X8" s="1">
         <v>1</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>428</v>
+        <v>376</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>433</v>
+        <v>381</v>
       </c>
       <c r="AA8" s="1" t="s">
-        <v>435</v>
+        <v>383</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
@@ -6127,7 +5991,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>110</v>
@@ -6136,7 +6000,7 @@
         <v>111</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>113</v>
@@ -6145,7 +6009,7 @@
         <v>114</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>149</v>
+        <v>401</v>
       </c>
       <c r="I9" s="1">
         <v>77</v>
@@ -6184,31 +6048,31 @@
         <v>不采购</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="U9" s="1">
         <v>0</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="X9" s="1">
         <v>1</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>412</v>
+        <v>360</v>
       </c>
       <c r="AA9" s="1" t="s">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="AB9" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
@@ -6216,7 +6080,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>110</v>
@@ -6228,13 +6092,13 @@
         <v>112</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>138</v>
+        <v>398</v>
       </c>
       <c r="I10" s="1">
         <v>83</v>
@@ -6273,31 +6137,31 @@
         <v>采购</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="U10" s="1">
         <v>1</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="X10" s="1">
         <v>1</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>301</v>
+        <v>261</v>
       </c>
       <c r="AA10" s="1" t="s">
-        <v>288</v>
+        <v>248</v>
       </c>
       <c r="AB10" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
@@ -6305,7 +6169,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>110</v>
@@ -6317,13 +6181,13 @@
         <v>112</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>142</v>
+        <v>399</v>
       </c>
       <c r="I11" s="1">
         <v>76</v>
@@ -6362,31 +6226,31 @@
         <v>不采购</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="U11" s="1">
         <v>0</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="X11" s="1">
         <v>1</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>302</v>
+        <v>262</v>
       </c>
       <c r="AA11" s="1" t="s">
-        <v>303</v>
+        <v>263</v>
       </c>
       <c r="AB11" s="1" t="s">
-        <v>292</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
@@ -6394,7 +6258,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>110</v>
@@ -6406,13 +6270,13 @@
         <v>112</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>146</v>
+        <v>400</v>
       </c>
       <c r="I12" s="1">
         <v>71</v>
@@ -6451,31 +6315,31 @@
         <v>不采购</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="U12" s="1">
         <v>0</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="X12" s="1">
         <v>1</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>304</v>
+        <v>264</v>
       </c>
       <c r="AA12" s="1" t="s">
-        <v>305</v>
+        <v>265</v>
       </c>
       <c r="AB12" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
@@ -6483,7 +6347,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>110</v>
@@ -6495,13 +6359,13 @@
         <v>112</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>149</v>
+        <v>401</v>
       </c>
       <c r="I13" s="1">
         <v>68</v>
@@ -6540,31 +6404,31 @@
         <v>不采购</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="U13" s="1">
         <v>0</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="X13" s="1">
         <v>1</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>306</v>
+        <v>266</v>
       </c>
       <c r="AA13" s="1" t="s">
-        <v>307</v>
+        <v>267</v>
       </c>
       <c r="AB13" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
@@ -6572,7 +6436,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>110</v>
@@ -6581,16 +6445,16 @@
         <v>111</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>158</v>
+        <v>409</v>
       </c>
       <c r="I14" s="1">
         <v>63</v>
@@ -6629,16 +6493,16 @@
         <v>不采购</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="U14" s="1">
         <v>1</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="X14" s="1">
         <v>0</v>
@@ -6647,13 +6511,13 @@
         <v>117</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>432</v>
+        <v>380</v>
       </c>
       <c r="AA14" s="1" t="s">
-        <v>434</v>
+        <v>382</v>
       </c>
       <c r="AB14" s="1" t="s">
-        <v>292</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.25">
@@ -6661,7 +6525,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>110</v>
@@ -6670,16 +6534,16 @@
         <v>111</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="H15" s="1" t="s">
-        <v>160</v>
+        <v>405</v>
       </c>
       <c r="I15" s="1">
         <v>61</v>
@@ -6718,31 +6582,31 @@
         <v>不采购</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="U15" s="1">
         <v>0</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="X15" s="1">
         <v>1</v>
       </c>
       <c r="Y15" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>309</v>
+        <v>269</v>
       </c>
       <c r="AA15" s="1" t="s">
-        <v>310</v>
+        <v>270</v>
       </c>
       <c r="AB15" s="1" t="s">
-        <v>292</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
@@ -6750,7 +6614,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>110</v>
@@ -6759,16 +6623,16 @@
         <v>111</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>163</v>
+        <v>407</v>
       </c>
       <c r="I16" s="1">
         <v>57</v>
@@ -6807,16 +6671,16 @@
         <v>不采购</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="U16" s="1">
         <v>1</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="X16" s="1">
         <v>0</v>
@@ -6825,13 +6689,13 @@
         <v>117</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>311</v>
+        <v>271</v>
       </c>
       <c r="AA16" s="1" t="s">
-        <v>312</v>
+        <v>272</v>
       </c>
       <c r="AB16" s="1" t="s">
-        <v>292</v>
+        <v>252</v>
       </c>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
@@ -6839,7 +6703,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>110</v>
@@ -6848,16 +6712,16 @@
         <v>111</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="H17" s="1" t="s">
-        <v>165</v>
+        <v>403</v>
       </c>
       <c r="I17" s="1">
         <v>54</v>
@@ -6896,31 +6760,31 @@
         <v>不采购</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="U17" s="1">
         <v>0</v>
       </c>
       <c r="V17" s="1" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="X17" s="1">
         <v>1</v>
       </c>
       <c r="Y17" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>313</v>
+        <v>273</v>
       </c>
       <c r="AA17" s="1" t="s">
-        <v>314</v>
+        <v>274</v>
       </c>
       <c r="AB17" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.25">
@@ -6928,13 +6792,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>112</v>
@@ -6946,7 +6810,7 @@
         <v>114</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>170</v>
+        <v>410</v>
       </c>
       <c r="I18" s="1">
         <v>92</v>
@@ -6985,31 +6849,31 @@
         <v>采购</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="U18" s="1">
         <v>1</v>
       </c>
       <c r="V18" s="1" t="s">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="X18" s="1">
         <v>1</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>284</v>
+        <v>244</v>
       </c>
       <c r="AA18" s="1" t="s">
-        <v>315</v>
+        <v>275</v>
       </c>
       <c r="AB18" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.25">
@@ -7017,13 +6881,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>112</v>
@@ -7035,7 +6899,7 @@
         <v>114</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>174</v>
+        <v>411</v>
       </c>
       <c r="I19" s="1">
         <v>85</v>
@@ -7074,31 +6938,31 @@
         <v>采购</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="U19" s="1">
         <v>1</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="X19" s="1">
         <v>1</v>
       </c>
       <c r="Y19" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z19" s="1" t="s">
-        <v>287</v>
+        <v>247</v>
       </c>
       <c r="AA19" s="1" t="s">
-        <v>316</v>
+        <v>276</v>
       </c>
       <c r="AB19" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
@@ -7106,13 +6970,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>112</v>
@@ -7124,7 +6988,7 @@
         <v>114</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>176</v>
+        <v>412</v>
       </c>
       <c r="I20" s="1">
         <v>78</v>
@@ -7163,31 +7027,31 @@
         <v>采购</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="U20" s="1">
         <v>1</v>
       </c>
       <c r="V20" s="1" t="s">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="X20" s="1">
         <v>1</v>
       </c>
       <c r="Y20" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z20" s="1" t="s">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="AA20" s="1" t="s">
-        <v>317</v>
+        <v>277</v>
       </c>
       <c r="AB20" s="1" t="s">
-        <v>292</v>
+        <v>252</v>
       </c>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
@@ -7195,13 +7059,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>112</v>
@@ -7213,7 +7077,7 @@
         <v>114</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>178</v>
+        <v>413</v>
       </c>
       <c r="I21" s="1">
         <v>72</v>
@@ -7252,31 +7116,31 @@
         <v>不采购</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="U21" s="1">
         <v>0</v>
       </c>
       <c r="V21" s="1" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="X21" s="1">
         <v>1</v>
       </c>
       <c r="Y21" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z21" s="1" t="s">
-        <v>294</v>
+        <v>254</v>
       </c>
       <c r="AA21" s="1" t="s">
-        <v>318</v>
+        <v>278</v>
       </c>
       <c r="AB21" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.25">
@@ -7284,16 +7148,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>113</v>
@@ -7302,7 +7166,7 @@
         <v>114</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>184</v>
+        <v>415</v>
       </c>
       <c r="I22" s="1">
         <v>66</v>
@@ -7341,31 +7205,31 @@
         <v>不采购</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="U22" s="1">
         <v>0</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="X22" s="1">
         <v>1</v>
       </c>
       <c r="Y22" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>296</v>
+        <v>256</v>
       </c>
       <c r="AA22" s="1" t="s">
-        <v>436</v>
+        <v>384</v>
       </c>
       <c r="AB22" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.25">
@@ -7373,16 +7237,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>113</v>
@@ -7391,7 +7255,7 @@
         <v>114</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>188</v>
+        <v>417</v>
       </c>
       <c r="I23" s="1">
         <v>59</v>
@@ -7430,31 +7294,31 @@
         <v>不采购</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="U23" s="1">
         <v>0</v>
       </c>
       <c r="V23" s="1" t="s">
-        <v>429</v>
+        <v>377</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="X23" s="1">
         <v>1</v>
       </c>
       <c r="Y23" s="1" t="s">
-        <v>428</v>
+        <v>376</v>
       </c>
       <c r="Z23" s="1" t="s">
-        <v>430</v>
+        <v>378</v>
       </c>
       <c r="AA23" s="1" t="s">
-        <v>437</v>
+        <v>385</v>
       </c>
       <c r="AB23" s="1" t="s">
-        <v>292</v>
+        <v>252</v>
       </c>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.25">
@@ -7462,16 +7326,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>113</v>
@@ -7480,7 +7344,7 @@
         <v>114</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>191</v>
+        <v>419</v>
       </c>
       <c r="I24" s="1">
         <v>52</v>
@@ -7519,31 +7383,31 @@
         <v>不采购</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="U24" s="1">
         <v>0</v>
       </c>
       <c r="V24" s="1" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="X24" s="1">
         <v>1</v>
       </c>
       <c r="Y24" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z24" s="1" t="s">
-        <v>298</v>
+        <v>258</v>
       </c>
       <c r="AA24" s="1" t="s">
-        <v>319</v>
+        <v>279</v>
       </c>
       <c r="AB24" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.25">
@@ -7551,16 +7415,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>113</v>
@@ -7569,7 +7433,7 @@
         <v>114</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>197</v>
+        <v>421</v>
       </c>
       <c r="I25" s="1">
         <v>44</v>
@@ -7608,31 +7472,31 @@
         <v>不采购</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="U25" s="1">
         <v>0</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="X25" s="1">
         <v>1</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>299</v>
+        <v>259</v>
       </c>
       <c r="AA25" s="1" t="s">
-        <v>320</v>
+        <v>280</v>
       </c>
       <c r="AB25" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="26" spans="1:28" x14ac:dyDescent="0.25">
@@ -7640,25 +7504,25 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>112</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>199</v>
+        <v>422</v>
       </c>
       <c r="I26" s="1">
         <v>83</v>
@@ -7697,31 +7561,31 @@
         <v>采购</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="U26" s="1">
         <v>1</v>
       </c>
       <c r="V26" s="1" t="s">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="X26" s="1">
         <v>1</v>
       </c>
       <c r="Y26" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>301</v>
+        <v>261</v>
       </c>
       <c r="AA26" s="1" t="s">
-        <v>316</v>
+        <v>276</v>
       </c>
       <c r="AB26" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.25">
@@ -7729,25 +7593,25 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>112</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>201</v>
+        <v>423</v>
       </c>
       <c r="I27" s="1">
         <v>76</v>
@@ -7786,31 +7650,31 @@
         <v>不采购</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="U27" s="1">
         <v>0</v>
       </c>
       <c r="V27" s="1" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="X27" s="1">
         <v>1</v>
       </c>
       <c r="Y27" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z27" s="1" t="s">
-        <v>302</v>
+        <v>262</v>
       </c>
       <c r="AA27" s="1" t="s">
-        <v>321</v>
+        <v>281</v>
       </c>
       <c r="AB27" s="1" t="s">
-        <v>292</v>
+        <v>252</v>
       </c>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.25">
@@ -7818,25 +7682,25 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>112</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>203</v>
+        <v>424</v>
       </c>
       <c r="I28" s="1">
         <v>71</v>
@@ -7875,31 +7739,31 @@
         <v>不采购</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="U28" s="1">
         <v>0</v>
       </c>
       <c r="V28" s="1" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="X28" s="1">
         <v>1</v>
       </c>
       <c r="Y28" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z28" s="1" t="s">
-        <v>304</v>
+        <v>264</v>
       </c>
       <c r="AA28" s="1" t="s">
-        <v>319</v>
+        <v>279</v>
       </c>
       <c r="AB28" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.25">
@@ -7907,25 +7771,25 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>112</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>206</v>
+        <v>425</v>
       </c>
       <c r="I29" s="1">
         <v>68</v>
@@ -7964,31 +7828,31 @@
         <v>不采购</v>
       </c>
       <c r="T29" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="U29" s="1">
+        <v>0</v>
+      </c>
+      <c r="V29" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="W29" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="X29" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y29" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z29" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="U29" s="1">
-        <v>0</v>
-      </c>
-      <c r="V29" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="W29" s="1" t="s">
+      <c r="AA29" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="X29" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y29" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="Z29" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="AA29" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="AB29" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="30" spans="1:28" x14ac:dyDescent="0.25">
@@ -7996,25 +7860,25 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>210</v>
+        <v>427</v>
       </c>
       <c r="I30" s="1">
         <v>63</v>
@@ -8053,16 +7917,16 @@
         <v>不采购</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="U30" s="1">
         <v>1</v>
       </c>
       <c r="V30" s="1" t="s">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="X30" s="1">
         <v>0</v>
@@ -8071,13 +7935,13 @@
         <v>117</v>
       </c>
       <c r="Z30" s="1" t="s">
-        <v>308</v>
+        <v>268</v>
       </c>
       <c r="AA30" s="1" t="s">
-        <v>324</v>
+        <v>284</v>
       </c>
       <c r="AB30" s="1" t="s">
-        <v>292</v>
+        <v>252</v>
       </c>
     </row>
     <row r="31" spans="1:28" x14ac:dyDescent="0.25">
@@ -8085,25 +7949,25 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>211</v>
+        <v>186</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>214</v>
+        <v>429</v>
       </c>
       <c r="I31" s="1">
         <v>61</v>
@@ -8142,31 +8006,31 @@
         <v>不采购</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="U31" s="1">
         <v>0</v>
       </c>
       <c r="V31" s="1" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="X31" s="1">
         <v>1</v>
       </c>
       <c r="Y31" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z31" s="1" t="s">
-        <v>325</v>
+        <v>285</v>
       </c>
       <c r="AA31" s="1" t="s">
-        <v>326</v>
+        <v>286</v>
       </c>
       <c r="AB31" s="1" t="s">
-        <v>292</v>
+        <v>252</v>
       </c>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.25">
@@ -8174,25 +8038,25 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>217</v>
+        <v>431</v>
       </c>
       <c r="I32" s="1">
         <v>57</v>
@@ -8231,16 +8095,16 @@
         <v>不采购</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="U32" s="1">
         <v>1</v>
       </c>
       <c r="V32" s="1" t="s">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="W32" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="X32" s="1">
         <v>0</v>
@@ -8249,13 +8113,13 @@
         <v>117</v>
       </c>
       <c r="Z32" s="1" t="s">
-        <v>311</v>
+        <v>271</v>
       </c>
       <c r="AA32" s="1" t="s">
-        <v>327</v>
+        <v>287</v>
       </c>
       <c r="AB32" s="1" t="s">
-        <v>292</v>
+        <v>252</v>
       </c>
     </row>
     <row r="33" spans="1:28" x14ac:dyDescent="0.25">
@@ -8263,25 +8127,25 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>221</v>
+        <v>433</v>
       </c>
       <c r="I33" s="1">
         <v>54</v>
@@ -8320,31 +8184,31 @@
         <v>不采购</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="U33" s="1">
         <v>0</v>
       </c>
       <c r="V33" s="1" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="X33" s="1">
         <v>1</v>
       </c>
       <c r="Y33" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z33" s="1" t="s">
-        <v>313</v>
+        <v>273</v>
       </c>
       <c r="AA33" s="1" t="s">
-        <v>328</v>
+        <v>288</v>
       </c>
       <c r="AB33" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="34" spans="1:28" x14ac:dyDescent="0.25">
@@ -8352,13 +8216,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>222</v>
+        <v>194</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>112</v>
@@ -8370,7 +8234,7 @@
         <v>114</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>227</v>
+        <v>434</v>
       </c>
       <c r="I34" s="1">
         <v>92</v>
@@ -8409,31 +8273,31 @@
         <v>采购</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="U34" s="1">
         <v>1</v>
       </c>
       <c r="V34" s="1" t="s">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="X34" s="1">
         <v>1</v>
       </c>
       <c r="Y34" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z34" s="1" t="s">
-        <v>284</v>
+        <v>244</v>
       </c>
       <c r="AA34" s="1" t="s">
-        <v>329</v>
+        <v>289</v>
       </c>
       <c r="AB34" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="35" spans="1:28" x14ac:dyDescent="0.25">
@@ -8441,13 +8305,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>228</v>
+        <v>199</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>112</v>
@@ -8459,7 +8323,7 @@
         <v>114</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>230</v>
+        <v>435</v>
       </c>
       <c r="I35" s="1">
         <v>85</v>
@@ -8498,31 +8362,31 @@
         <v>采购</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="U35" s="1">
         <v>1</v>
       </c>
       <c r="V35" s="1" t="s">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="X35" s="1">
         <v>1</v>
       </c>
       <c r="Y35" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z35" s="1" t="s">
-        <v>287</v>
+        <v>247</v>
       </c>
       <c r="AA35" s="1" t="s">
-        <v>330</v>
+        <v>290</v>
       </c>
       <c r="AB35" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="36" spans="1:28" x14ac:dyDescent="0.25">
@@ -8530,13 +8394,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>112</v>
@@ -8548,7 +8412,7 @@
         <v>114</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>232</v>
+        <v>436</v>
       </c>
       <c r="I36" s="1">
         <v>78</v>
@@ -8587,31 +8451,31 @@
         <v>采购</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="U36" s="1">
         <v>1</v>
       </c>
       <c r="V36" s="1" t="s">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>331</v>
+        <v>291</v>
       </c>
       <c r="X36" s="1">
         <v>1</v>
       </c>
       <c r="Y36" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z36" s="1" t="s">
-        <v>414</v>
+        <v>362</v>
       </c>
       <c r="AA36" s="1" t="s">
-        <v>416</v>
+        <v>364</v>
       </c>
       <c r="AB36" s="1" t="s">
-        <v>332</v>
+        <v>292</v>
       </c>
     </row>
     <row r="37" spans="1:28" x14ac:dyDescent="0.25">
@@ -8619,13 +8483,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>233</v>
+        <v>202</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>112</v>
@@ -8637,7 +8501,7 @@
         <v>114</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>234</v>
+        <v>437</v>
       </c>
       <c r="I37" s="1">
         <v>72</v>
@@ -8676,31 +8540,31 @@
         <v>不采购</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="U37" s="1">
         <v>0</v>
       </c>
       <c r="V37" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="W37" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="X37" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y37" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z37" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="W37" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="X37" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y37" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="Z37" s="1" t="s">
-        <v>333</v>
-      </c>
       <c r="AA37" s="1" t="s">
-        <v>334</v>
+        <v>294</v>
       </c>
       <c r="AB37" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="38" spans="1:28" x14ac:dyDescent="0.25">
@@ -8708,16 +8572,16 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>235</v>
+        <v>203</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>236</v>
+        <v>204</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>113</v>
@@ -8726,7 +8590,7 @@
         <v>114</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>240</v>
+        <v>439</v>
       </c>
       <c r="I38" s="1">
         <v>66</v>
@@ -8765,31 +8629,31 @@
         <v>不采购</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="U38" s="1">
         <v>0</v>
       </c>
       <c r="V38" s="1" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="W38" s="1" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="X38" s="1">
         <v>1</v>
       </c>
       <c r="Y38" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z38" s="1" t="s">
-        <v>335</v>
+        <v>295</v>
       </c>
       <c r="AA38" s="1" t="s">
-        <v>423</v>
+        <v>371</v>
       </c>
       <c r="AB38" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="39" spans="1:28" x14ac:dyDescent="0.25">
@@ -8797,16 +8661,16 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>241</v>
+        <v>208</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>113</v>
@@ -8815,7 +8679,7 @@
         <v>114</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>246</v>
+        <v>441</v>
       </c>
       <c r="I39" s="1">
         <v>59</v>
@@ -8854,31 +8718,31 @@
         <v>不采购</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="U39" s="1">
         <v>0</v>
       </c>
       <c r="V39" s="1" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="W39" s="1" t="s">
-        <v>331</v>
+        <v>291</v>
       </c>
       <c r="X39" s="1">
         <v>1</v>
       </c>
       <c r="Y39" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z39" s="1" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="AA39" s="1" t="s">
-        <v>424</v>
+        <v>372</v>
       </c>
       <c r="AB39" s="1" t="s">
-        <v>332</v>
+        <v>292</v>
       </c>
     </row>
     <row r="40" spans="1:28" x14ac:dyDescent="0.25">
@@ -8886,16 +8750,16 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>247</v>
+        <v>213</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>113</v>
@@ -8904,7 +8768,7 @@
         <v>114</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>248</v>
+        <v>443</v>
       </c>
       <c r="I40" s="1">
         <v>52</v>
@@ -8943,31 +8807,31 @@
         <v>不采购</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="U40" s="1">
         <v>0</v>
       </c>
       <c r="V40" s="1" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="W40" s="1" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="X40" s="1">
         <v>1</v>
       </c>
       <c r="Y40" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z40" s="1" t="s">
-        <v>336</v>
+        <v>296</v>
       </c>
       <c r="AA40" s="1" t="s">
-        <v>337</v>
+        <v>297</v>
       </c>
       <c r="AB40" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="41" spans="1:28" x14ac:dyDescent="0.25">
@@ -8975,16 +8839,16 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>249</v>
+        <v>214</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>113</v>
@@ -8993,7 +8857,7 @@
         <v>114</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>252</v>
+        <v>445</v>
       </c>
       <c r="I41" s="1">
         <v>44</v>
@@ -9032,31 +8896,31 @@
         <v>不采购</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="U41" s="1">
         <v>0</v>
       </c>
       <c r="V41" s="1" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="W41" s="1" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="X41" s="1">
         <v>1</v>
       </c>
       <c r="Y41" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z41" s="1" t="s">
-        <v>299</v>
+        <v>259</v>
       </c>
       <c r="AA41" s="1" t="s">
-        <v>338</v>
+        <v>298</v>
       </c>
       <c r="AB41" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="42" spans="1:28" x14ac:dyDescent="0.25">
@@ -9064,25 +8928,25 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>253</v>
+        <v>217</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E42" t="s">
-        <v>394</v>
+        <v>346</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H42" t="s">
-        <v>405</v>
+        <v>446</v>
       </c>
       <c r="I42" s="1">
         <v>83</v>
@@ -9121,16 +8985,16 @@
         <v>采购</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="U42" s="1">
         <v>0</v>
       </c>
       <c r="V42" s="1" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="W42" s="1" t="s">
-        <v>331</v>
+        <v>291</v>
       </c>
       <c r="X42" s="1">
         <v>0</v>
@@ -9139,13 +9003,13 @@
         <v>117</v>
       </c>
       <c r="Z42" s="1" t="s">
-        <v>339</v>
+        <v>299</v>
       </c>
       <c r="AA42" s="1" t="s">
-        <v>417</v>
+        <v>365</v>
       </c>
       <c r="AB42" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="43" spans="1:28" x14ac:dyDescent="0.25">
@@ -9153,25 +9017,25 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>257</v>
+        <v>220</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E43" t="s">
-        <v>394</v>
+        <v>346</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H43" t="s">
-        <v>406</v>
+        <v>447</v>
       </c>
       <c r="I43" s="1">
         <v>76</v>
@@ -9210,31 +9074,31 @@
         <v>不采购</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="U43" s="1">
         <v>0</v>
       </c>
       <c r="V43" s="1" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="W43" s="1" t="s">
-        <v>331</v>
+        <v>291</v>
       </c>
       <c r="X43" s="1">
         <v>1</v>
       </c>
       <c r="Y43" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z43" s="1" t="s">
-        <v>415</v>
+        <v>363</v>
       </c>
       <c r="AA43" s="1" t="s">
-        <v>418</v>
+        <v>366</v>
       </c>
       <c r="AB43" s="1" t="s">
-        <v>332</v>
+        <v>292</v>
       </c>
     </row>
     <row r="44" spans="1:28" x14ac:dyDescent="0.25">
@@ -9242,25 +9106,25 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>262</v>
+        <v>224</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E44" t="s">
-        <v>236</v>
+        <v>204</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H44" t="s">
-        <v>263</v>
+        <v>449</v>
       </c>
       <c r="I44" s="1">
         <v>71</v>
@@ -9299,31 +9163,31 @@
         <v>不采购</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="U44" s="1">
         <v>0</v>
       </c>
       <c r="V44" s="1" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="W44" s="1" t="s">
-        <v>331</v>
+        <v>291</v>
       </c>
       <c r="X44" s="1">
         <v>1</v>
       </c>
       <c r="Y44" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z44" s="1" t="s">
-        <v>420</v>
+        <v>368</v>
       </c>
       <c r="AA44" s="1" t="s">
-        <v>425</v>
+        <v>373</v>
       </c>
       <c r="AB44" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="45" spans="1:28" x14ac:dyDescent="0.25">
@@ -9331,25 +9195,25 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>264</v>
+        <v>225</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E45" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H45" t="s">
-        <v>268</v>
+        <v>451</v>
       </c>
       <c r="I45" s="1">
         <v>68</v>
@@ -9388,31 +9252,31 @@
         <v>不采购</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="U45" s="1">
         <v>0</v>
       </c>
       <c r="V45" s="1" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="W45" s="1" t="s">
-        <v>331</v>
+        <v>291</v>
       </c>
       <c r="X45" s="1">
         <v>1</v>
       </c>
       <c r="Y45" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z45" s="1" t="s">
-        <v>421</v>
+        <v>369</v>
       </c>
       <c r="AA45" s="1" t="s">
-        <v>426</v>
+        <v>374</v>
       </c>
       <c r="AB45" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="46" spans="1:28" x14ac:dyDescent="0.25">
@@ -9420,25 +9284,25 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>269</v>
+        <v>229</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E46" t="s">
-        <v>236</v>
+        <v>204</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H46" t="s">
-        <v>256</v>
+        <v>453</v>
       </c>
       <c r="I46" s="1">
         <v>63</v>
@@ -9477,31 +9341,31 @@
         <v>不采购</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="U46" s="1">
         <v>0</v>
       </c>
       <c r="V46" s="1" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="W46" s="1" t="s">
-        <v>331</v>
+        <v>291</v>
       </c>
       <c r="X46" s="1">
         <v>1</v>
       </c>
       <c r="Y46" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z46" s="1" t="s">
-        <v>422</v>
+        <v>370</v>
       </c>
       <c r="AA46" s="1" t="s">
-        <v>427</v>
+        <v>375</v>
       </c>
       <c r="AB46" s="1" t="s">
-        <v>332</v>
+        <v>292</v>
       </c>
     </row>
     <row r="47" spans="1:28" x14ac:dyDescent="0.25">
@@ -9509,25 +9373,25 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>270</v>
+        <v>230</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E47" t="s">
-        <v>265</v>
+        <v>226</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H47" t="s">
-        <v>261</v>
+        <v>455</v>
       </c>
       <c r="I47" s="1">
         <v>61</v>
@@ -9566,16 +9430,16 @@
         <v>不采购</v>
       </c>
       <c r="T47" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="U47" s="1">
         <v>1</v>
       </c>
       <c r="V47" s="1" t="s">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="W47" s="1" t="s">
-        <v>331</v>
+        <v>291</v>
       </c>
       <c r="X47" s="1">
         <v>0</v>
@@ -9584,13 +9448,13 @@
         <v>117</v>
       </c>
       <c r="Z47" s="1" t="s">
-        <v>340</v>
+        <v>300</v>
       </c>
       <c r="AA47" s="1" t="s">
-        <v>341</v>
+        <v>301</v>
       </c>
       <c r="AB47" s="1" t="s">
-        <v>332</v>
+        <v>292</v>
       </c>
     </row>
     <row r="48" spans="1:28" x14ac:dyDescent="0.25">
@@ -9598,25 +9462,25 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>271</v>
+        <v>231</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E48" t="s">
-        <v>394</v>
+        <v>346</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H48" t="s">
-        <v>407</v>
+        <v>456</v>
       </c>
       <c r="I48" s="1">
         <v>57</v>
@@ -9655,16 +9519,16 @@
         <v>不采购</v>
       </c>
       <c r="T48" s="1" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="U48" s="1">
         <v>1</v>
       </c>
       <c r="V48" s="1" t="s">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="W48" s="1" t="s">
-        <v>331</v>
+        <v>291</v>
       </c>
       <c r="X48" s="1">
         <v>0</v>
@@ -9673,13 +9537,13 @@
         <v>117</v>
       </c>
       <c r="Z48" s="1" t="s">
-        <v>311</v>
+        <v>271</v>
       </c>
       <c r="AA48" s="1" t="s">
-        <v>342</v>
+        <v>302</v>
       </c>
       <c r="AB48" s="1" t="s">
-        <v>332</v>
+        <v>292</v>
       </c>
     </row>
     <row r="49" spans="1:28" x14ac:dyDescent="0.25">
@@ -9687,25 +9551,25 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>272</v>
+        <v>232</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E49" t="s">
-        <v>394</v>
+        <v>346</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H49" t="s">
-        <v>408</v>
+        <v>457</v>
       </c>
       <c r="I49" s="1">
         <v>54</v>
@@ -9744,16 +9608,16 @@
         <v>不采购</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="U49" s="1">
         <v>1</v>
       </c>
       <c r="V49" s="1" t="s">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="W49" s="1" t="s">
-        <v>331</v>
+        <v>291</v>
       </c>
       <c r="X49" s="1">
         <v>0</v>
@@ -9762,13 +9626,13 @@
         <v>117</v>
       </c>
       <c r="Z49" s="1" t="s">
-        <v>343</v>
+        <v>303</v>
       </c>
       <c r="AA49" s="1" t="s">
-        <v>344</v>
+        <v>304</v>
       </c>
       <c r="AB49" s="1" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -9790,15 +9654,15 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>345</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>346</v>
+        <v>306</v>
       </c>
       <c r="B3" t="s">
-        <v>347</v>
+        <v>307</v>
       </c>
       <c r="C3" t="s">
         <v>39</v>
@@ -9816,13 +9680,13 @@
         <v>44</v>
       </c>
       <c r="H3" t="s">
-        <v>348</v>
+        <v>308</v>
       </c>
       <c r="I3" t="s">
-        <v>349</v>
+        <v>309</v>
       </c>
       <c r="J3" t="s">
-        <v>350</v>
+        <v>310</v>
       </c>
       <c r="K3" t="s">
         <v>102</v>
@@ -9831,7 +9695,7 @@
         <v>60</v>
       </c>
       <c r="M3" t="s">
-        <v>351</v>
+        <v>311</v>
       </c>
       <c r="N3" t="s">
         <v>11</v>
@@ -9842,7 +9706,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>352</v>
+        <v>312</v>
       </c>
       <c r="C4" t="s">
         <v>109</v>
@@ -9857,10 +9721,10 @@
         <v>113</v>
       </c>
       <c r="G4" t="s">
-        <v>353</v>
+        <v>458</v>
       </c>
       <c r="H4" t="s">
-        <v>354</v>
+        <v>313</v>
       </c>
       <c r="I4" t="s">
         <v>115</v>
@@ -9875,10 +9739,10 @@
         <v>1</v>
       </c>
       <c r="M4" t="s">
-        <v>355</v>
+        <v>314</v>
       </c>
       <c r="N4" t="s">
-        <v>356</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -9886,25 +9750,25 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>352</v>
+        <v>312</v>
       </c>
       <c r="C5" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="D5" t="s">
         <v>111</v>
       </c>
       <c r="E5" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F5" t="s">
         <v>113</v>
       </c>
       <c r="G5" t="s">
-        <v>357</v>
+        <v>459</v>
       </c>
       <c r="H5" t="s">
-        <v>354</v>
+        <v>313</v>
       </c>
       <c r="I5" t="s">
         <v>116</v>
@@ -9919,10 +9783,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="s">
-        <v>374</v>
+        <v>326</v>
       </c>
       <c r="N5" t="s">
-        <v>356</v>
+        <v>315</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -9930,13 +9794,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>352</v>
+        <v>312</v>
       </c>
       <c r="C6" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="D6" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E6" t="s">
         <v>112</v>
@@ -9945,10 +9809,10 @@
         <v>113</v>
       </c>
       <c r="G6" t="s">
-        <v>358</v>
+        <v>460</v>
       </c>
       <c r="H6" t="s">
-        <v>354</v>
+        <v>313</v>
       </c>
       <c r="I6" t="s">
         <v>115</v>
@@ -9963,10 +9827,10 @@
         <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>359</v>
+        <v>316</v>
       </c>
       <c r="N6" t="s">
-        <v>356</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -9974,25 +9838,25 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>352</v>
+        <v>312</v>
       </c>
       <c r="C7" t="s">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="D7" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E7" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="F7" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G7" t="s">
-        <v>360</v>
+        <v>461</v>
       </c>
       <c r="H7" t="s">
-        <v>354</v>
+        <v>313</v>
       </c>
       <c r="I7" t="s">
         <v>116</v>
@@ -10007,10 +9871,10 @@
         <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>359</v>
+        <v>316</v>
       </c>
       <c r="N7" t="s">
-        <v>356</v>
+        <v>315</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -10018,10 +9882,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>361</v>
+        <v>317</v>
       </c>
       <c r="C8" t="s">
-        <v>362</v>
+        <v>318</v>
       </c>
       <c r="D8" t="s">
         <v>111</v>
@@ -10033,28 +9897,28 @@
         <v>113</v>
       </c>
       <c r="G8" t="s">
-        <v>363</v>
+        <v>462</v>
       </c>
       <c r="H8" t="s">
-        <v>364</v>
+        <v>319</v>
       </c>
       <c r="I8" t="s">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="J8">
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="L8">
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>365</v>
+        <v>320</v>
       </c>
       <c r="N8" t="s">
-        <v>356</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -10062,43 +9926,43 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>361</v>
+        <v>317</v>
       </c>
       <c r="C9" t="s">
-        <v>366</v>
+        <v>321</v>
       </c>
       <c r="D9" t="s">
         <v>111</v>
       </c>
       <c r="E9" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F9" t="s">
         <v>113</v>
       </c>
       <c r="G9" t="s">
-        <v>367</v>
+        <v>463</v>
       </c>
       <c r="H9" t="s">
-        <v>364</v>
+        <v>319</v>
       </c>
       <c r="I9" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9" t="s">
-        <v>368</v>
+        <v>322</v>
       </c>
       <c r="N9" t="s">
-        <v>356</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -10106,43 +9970,43 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>361</v>
+        <v>317</v>
       </c>
       <c r="C10" t="s">
-        <v>369</v>
+        <v>323</v>
       </c>
       <c r="D10" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E10" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="F10" t="s">
         <v>113</v>
       </c>
       <c r="G10" t="s">
-        <v>370</v>
+        <v>464</v>
       </c>
       <c r="H10" t="s">
-        <v>364</v>
+        <v>319</v>
       </c>
       <c r="I10" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>371</v>
+        <v>324</v>
       </c>
       <c r="N10" t="s">
-        <v>356</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -10150,43 +10014,43 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>361</v>
+        <v>317</v>
       </c>
       <c r="C11" t="s">
-        <v>372</v>
+        <v>325</v>
       </c>
       <c r="D11" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E11" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="F11" t="s">
         <v>113</v>
       </c>
       <c r="G11" t="s">
-        <v>373</v>
+        <v>465</v>
       </c>
       <c r="H11" t="s">
-        <v>364</v>
+        <v>319</v>
       </c>
       <c r="I11" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11" t="s">
-        <v>409</v>
+        <v>357</v>
       </c>
       <c r="N11" t="s">
-        <v>356</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
